--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6605F5-F909-4065-92F0-4690F6A61AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2529,9 +2530,6 @@
     <t>ROSSELOT SANDRA MABEL</t>
   </si>
   <si>
-    <t>VERA MARIA JOS</t>
-  </si>
-  <si>
     <t>LEZCANO FONSALIDA VALERIA INES</t>
   </si>
   <si>
@@ -2740,12 +2738,15 @@
   </si>
   <si>
     <t>ZAMBRANO CASTRO ANGELO LEONELO</t>
+  </si>
+  <si>
+    <t>VERA MARIA JOSÉ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3056,7 +3057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6149,7 +6150,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>836</v>
+        <v>906</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -6157,7 +6158,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -6165,7 +6166,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -6173,7 +6174,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -6181,7 +6182,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -6189,7 +6190,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -6197,7 +6198,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -6205,7 +6206,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -6213,7 +6214,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -6221,7 +6222,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -6229,7 +6230,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -6237,7 +6238,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -6245,7 +6246,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -6253,7 +6254,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -6261,7 +6262,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -6269,7 +6270,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -6277,7 +6278,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -6285,7 +6286,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -6293,7 +6294,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -6301,7 +6302,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -6309,7 +6310,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -6317,7 +6318,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -6325,7 +6326,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -6333,7 +6334,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -6341,7 +6342,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -6349,7 +6350,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -6357,7 +6358,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -6365,7 +6366,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -6373,7 +6374,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -6381,7 +6382,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -6389,7 +6390,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -6397,7 +6398,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -6405,7 +6406,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -6413,7 +6414,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -6421,7 +6422,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -6429,7 +6430,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -6437,7 +6438,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -6445,7 +6446,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -6453,7 +6454,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -6461,7 +6462,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
@@ -6469,7 +6470,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
@@ -6477,7 +6478,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
@@ -6485,7 +6486,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -6493,7 +6494,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
@@ -6501,7 +6502,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
@@ -6509,7 +6510,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
@@ -6517,7 +6518,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -6525,7 +6526,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
@@ -6533,7 +6534,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
@@ -6541,7 +6542,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
@@ -6549,7 +6550,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
@@ -6557,7 +6558,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
@@ -6565,7 +6566,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
@@ -6573,7 +6574,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
@@ -6581,7 +6582,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
@@ -6589,7 +6590,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
@@ -6597,7 +6598,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
@@ -6605,7 +6606,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
@@ -6613,7 +6614,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
@@ -6621,7 +6622,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
@@ -6629,7 +6630,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
@@ -6637,7 +6638,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
@@ -6645,7 +6646,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
@@ -6653,7 +6654,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
@@ -6661,7 +6662,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
@@ -6669,7 +6670,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
@@ -6677,7 +6678,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
@@ -6685,7 +6686,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
@@ -6693,7 +6694,7 @@
         <v>41054898</v>
       </c>
       <c r="B454" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
@@ -6701,7 +6702,7 @@
         <v>41054263</v>
       </c>
       <c r="B455" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
@@ -6717,7 +6718,7 @@
         <v>37298216</v>
       </c>
       <c r="B457" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acreditaciones\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197C9AF7-BC7D-48FE-8C5D-1A8F384B82FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="851">
   <si>
     <t>DNI</t>
   </si>
@@ -1431,9 +1432,6 @@
     <t>ORTIZ ALICIA ELIZABETH</t>
   </si>
   <si>
-    <t>GAY MIGUEL ANGEL</t>
-  </si>
-  <si>
     <t>ABAD RAMIREZ ANA LAURA</t>
   </si>
   <si>
@@ -2566,12 +2564,21 @@
   </si>
   <si>
     <t>Nombre</t>
+  </si>
+  <si>
+    <t>GAYA MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>CORREA GUERRA AGUSTINA ROSALÌ</t>
+  </si>
+  <si>
+    <t>ANDRADA NATALIA GABRIELA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2925,8 +2932,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B425"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B427"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2934,7 +2941,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -3313,7 +3320,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>470</v>
+        <v>848</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -3321,7 +3328,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -3329,7 +3336,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -3337,7 +3344,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -3345,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -3353,7 +3360,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -3361,7 +3368,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -3369,7 +3376,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -3377,7 +3384,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -3385,7 +3392,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -3393,7 +3400,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -3401,7 +3408,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -3409,7 +3416,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -3417,7 +3424,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -3425,7 +3432,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -3433,7 +3440,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -3441,7 +3448,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -3449,7 +3456,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -3457,7 +3464,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -3465,7 +3472,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -3473,7 +3480,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -3481,7 +3488,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -3489,7 +3496,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -3497,7 +3504,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -3505,7 +3512,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -3513,7 +3520,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -3521,7 +3528,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -3529,7 +3536,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -3537,7 +3544,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -3545,7 +3552,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -3553,7 +3560,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -3561,7 +3568,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -3569,7 +3576,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -3577,7 +3584,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -3585,7 +3592,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -3593,7 +3600,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -3601,7 +3608,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -3609,7 +3616,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -3617,7 +3624,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -3625,7 +3632,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -3633,7 +3640,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -3641,7 +3648,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -3649,7 +3656,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -3657,7 +3664,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -3665,7 +3672,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -3673,7 +3680,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -3681,7 +3688,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -3689,7 +3696,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -3697,7 +3704,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -3705,7 +3712,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -3713,7 +3720,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -3721,7 +3728,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -3729,7 +3736,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -3737,7 +3744,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -3745,7 +3752,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -3753,7 +3760,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -3761,7 +3768,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -3769,7 +3776,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -3777,7 +3784,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -3785,7 +3792,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -3793,7 +3800,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -3801,7 +3808,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -3809,7 +3816,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -3817,7 +3824,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -3825,7 +3832,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -3833,7 +3840,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -3841,7 +3848,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -3849,7 +3856,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -3857,7 +3864,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -3865,7 +3872,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -3873,7 +3880,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -3881,7 +3888,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -3889,7 +3896,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -3897,7 +3904,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -3905,7 +3912,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -3913,7 +3920,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -3921,7 +3928,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -3929,7 +3936,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -3937,7 +3944,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -3945,7 +3952,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -3953,7 +3960,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -3961,7 +3968,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -3969,7 +3976,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3977,7 +3984,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3985,7 +3992,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3993,7 +4000,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -4001,7 +4008,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -4009,7 +4016,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -4017,7 +4024,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -4025,7 +4032,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -4033,7 +4040,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -4041,7 +4048,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -4049,7 +4056,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -4057,7 +4064,7 @@
         <v>26791373</v>
       </c>
       <c r="B141" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -4065,7 +4072,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -4073,7 +4080,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -4081,7 +4088,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -4089,7 +4096,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -4097,7 +4104,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -4105,7 +4112,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -4113,7 +4120,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -4121,7 +4128,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -4129,7 +4136,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -4137,7 +4144,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -4145,7 +4152,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -4153,7 +4160,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -4161,7 +4168,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -4169,7 +4176,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -4177,7 +4184,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -4185,7 +4192,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -4193,7 +4200,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -4201,7 +4208,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -4209,7 +4216,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -4217,7 +4224,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -4225,7 +4232,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -4233,7 +4240,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -4241,7 +4248,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -4249,7 +4256,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -4257,7 +4264,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -4265,7 +4272,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -4273,7 +4280,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -4281,7 +4288,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -4289,7 +4296,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -4297,7 +4304,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -4305,7 +4312,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -4313,7 +4320,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -4321,7 +4328,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -4329,7 +4336,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -4337,7 +4344,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -4345,7 +4352,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -4353,7 +4360,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -4361,7 +4368,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -4369,7 +4376,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -4377,7 +4384,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -4385,7 +4392,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -4393,7 +4400,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -4401,7 +4408,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -4409,7 +4416,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -4417,7 +4424,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -4425,7 +4432,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -4433,7 +4440,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -4441,7 +4448,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -4449,7 +4456,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -4457,7 +4464,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -4465,7 +4472,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -4473,7 +4480,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -4481,7 +4488,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -4489,7 +4496,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -4497,7 +4504,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -4505,7 +4512,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -4513,7 +4520,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -4521,7 +4528,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -4529,7 +4536,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -4537,7 +4544,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -4545,7 +4552,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -4553,7 +4560,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -4561,7 +4568,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -4569,7 +4576,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -4577,7 +4584,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -4585,7 +4592,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -4593,7 +4600,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -4601,7 +4608,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -4609,7 +4616,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -4617,7 +4624,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -4625,7 +4632,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -4633,7 +4640,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -4641,7 +4648,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -4649,7 +4656,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -4657,7 +4664,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -4665,7 +4672,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -4673,7 +4680,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -4681,7 +4688,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -4689,7 +4696,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -4697,7 +4704,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -4705,7 +4712,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -4713,7 +4720,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -4721,7 +4728,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -4729,7 +4736,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -4737,7 +4744,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -4745,7 +4752,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -4753,7 +4760,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -4761,7 +4768,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -4769,7 +4776,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -4777,7 +4784,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -4785,7 +4792,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -4793,7 +4800,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -4801,7 +4808,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -4809,7 +4816,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -4817,7 +4824,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -4825,7 +4832,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -4833,7 +4840,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -4841,7 +4848,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -4849,7 +4856,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -4857,7 +4864,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -4865,7 +4872,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -4873,7 +4880,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -4881,7 +4888,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -4889,7 +4896,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -4897,7 +4904,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -4905,7 +4912,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -4913,7 +4920,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -4921,7 +4928,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -4929,7 +4936,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -4937,7 +4944,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -4945,7 +4952,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -4953,7 +4960,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -4961,7 +4968,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -4969,7 +4976,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4977,7 +4984,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4985,7 +4992,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -4993,7 +5000,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -5001,7 +5008,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -5009,7 +5016,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -5017,7 +5024,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -5025,7 +5032,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -5033,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -5041,7 +5048,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -5049,7 +5056,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -5057,7 +5064,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -5065,7 +5072,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -5073,7 +5080,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -5081,7 +5088,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -5089,7 +5096,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -5097,7 +5104,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -5105,7 +5112,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -5113,7 +5120,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -5121,7 +5128,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -5129,7 +5136,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -5137,7 +5144,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -5145,7 +5152,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -5153,7 +5160,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -5161,7 +5168,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
@@ -5169,7 +5176,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
@@ -5177,7 +5184,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
@@ -5185,7 +5192,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -5193,7 +5200,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
@@ -5201,7 +5208,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
@@ -5209,7 +5216,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
@@ -5217,7 +5224,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
@@ -5225,7 +5232,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
@@ -5233,7 +5240,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
@@ -5241,7 +5248,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
@@ -5249,7 +5256,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
@@ -5257,7 +5264,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
@@ -5265,7 +5272,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
@@ -5273,7 +5280,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
@@ -5281,7 +5288,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
@@ -5289,7 +5296,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
@@ -5297,7 +5304,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
@@ -5305,7 +5312,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
@@ -5313,7 +5320,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
@@ -5321,7 +5328,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
@@ -5329,7 +5336,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
@@ -5337,7 +5344,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -5345,7 +5352,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -5353,7 +5360,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -5361,7 +5368,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -5369,7 +5376,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -5377,7 +5384,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -5385,7 +5392,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -5393,7 +5400,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -5401,7 +5408,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -5409,7 +5416,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -5417,7 +5424,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -5425,7 +5432,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -5433,7 +5440,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -5441,7 +5448,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -5449,7 +5456,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -5457,7 +5464,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -5465,7 +5472,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -5473,7 +5480,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -5481,7 +5488,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -5489,7 +5496,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -5497,7 +5504,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -5505,7 +5512,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -5513,7 +5520,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -5521,7 +5528,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -5529,7 +5536,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -5537,7 +5544,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -5545,7 +5552,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -5553,7 +5560,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -5561,7 +5568,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -5569,7 +5576,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -5577,7 +5584,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -5585,7 +5592,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -5593,7 +5600,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -5601,7 +5608,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
@@ -5609,7 +5616,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
@@ -5617,7 +5624,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
@@ -5625,7 +5632,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
@@ -5633,7 +5640,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
@@ -5641,7 +5648,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
@@ -5649,7 +5656,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
@@ -5657,7 +5664,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
@@ -5665,7 +5672,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
@@ -5673,7 +5680,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
@@ -5681,7 +5688,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
@@ -5689,7 +5696,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
@@ -5697,7 +5704,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
@@ -5705,7 +5712,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
@@ -5713,7 +5720,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
@@ -5721,7 +5728,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -5729,7 +5736,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
@@ -5737,7 +5744,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
@@ -5745,7 +5752,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
@@ -5753,7 +5760,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
@@ -5761,7 +5768,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
@@ -5769,7 +5776,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
@@ -5777,7 +5784,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
@@ -5785,7 +5792,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
@@ -5793,7 +5800,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
@@ -5801,7 +5808,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
@@ -5809,7 +5816,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
@@ -5817,7 +5824,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
@@ -5825,7 +5832,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
@@ -5833,7 +5840,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
@@ -5841,7 +5848,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
@@ -5849,7 +5856,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -5857,7 +5864,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
@@ -5865,7 +5872,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
@@ -5873,7 +5880,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
@@ -5881,7 +5888,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
@@ -5889,7 +5896,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
@@ -5897,7 +5904,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
@@ -5905,7 +5912,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
@@ -5913,7 +5920,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
@@ -5921,7 +5928,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
@@ -5929,7 +5936,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
@@ -5937,7 +5944,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
@@ -5945,7 +5952,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
@@ -5953,7 +5960,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
@@ -5961,7 +5968,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
@@ -5969,7 +5976,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
@@ -5977,7 +5984,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
@@ -5985,7 +5992,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -5993,7 +6000,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -6001,7 +6008,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
@@ -6009,7 +6016,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
@@ -6017,7 +6024,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -6025,7 +6032,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -6033,7 +6040,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -6041,7 +6048,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -6049,7 +6056,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -6057,7 +6064,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -6065,7 +6072,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -6073,7 +6080,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -6081,7 +6088,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -6089,7 +6096,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -6097,7 +6104,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -6105,7 +6112,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -6113,7 +6120,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -6121,7 +6128,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -6129,7 +6136,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -6137,7 +6144,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -6145,7 +6152,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -6153,7 +6160,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -6161,7 +6168,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -6169,7 +6176,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -6177,7 +6184,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -6185,7 +6192,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -6193,7 +6200,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -6201,7 +6208,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -6209,7 +6216,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -6217,7 +6224,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -6225,7 +6232,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -6233,7 +6240,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -6241,7 +6248,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -6249,7 +6256,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -6257,7 +6264,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -6265,7 +6272,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -6273,7 +6280,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -6281,7 +6288,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -6289,7 +6296,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -6297,7 +6304,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -6305,7 +6312,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -6313,7 +6320,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -6321,7 +6328,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -6329,7 +6336,23 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>847</v>
+        <v>846</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>39994394</v>
+      </c>
+      <c r="B426" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>26434505</v>
+      </c>
+      <c r="B427" t="s">
+        <v>850</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197C9AF7-BC7D-48FE-8C5D-1A8F384B82FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F178561A-FED9-4311-A1BA-A0977091F0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$428</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="852">
   <si>
     <t>DNI</t>
   </si>
@@ -1735,9 +1738,6 @@
     <t>PIZARRO VANESA NATALIA</t>
   </si>
   <si>
-    <t>DES CID LIA GUADALUPE</t>
-  </si>
-  <si>
     <t>FARIAS MUÑOZ GLADYS MIRTHA</t>
   </si>
   <si>
@@ -2167,9 +2167,6 @@
     <t>RODRIGUEZ MARTINEZ JESICA MARISEL</t>
   </si>
   <si>
-    <t>ROSSOMANDO MANCHADO PAOLA ANTONELLA</t>
-  </si>
-  <si>
     <t>CASIVAR CARLA MARIANA</t>
   </si>
   <si>
@@ -2573,6 +2570,15 @@
   </si>
   <si>
     <t>ANDRADA NATALIA GABRIELA</t>
+  </si>
+  <si>
+    <t>DEL CID LIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>URICHE MARCELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ROSSOMANDO PAOLA ANTONELLA</t>
   </si>
 </sst>
 </file>
@@ -2933,7 +2939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B427"/>
+  <dimension ref="A1:B428"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2941,7 +2947,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -3320,7 +3326,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4136,7 +4142,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>571</v>
+        <v>849</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -4144,7 +4150,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -4152,7 +4158,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -4160,7 +4166,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -4168,7 +4174,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -4176,7 +4182,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -4184,7 +4190,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -4192,7 +4198,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -4200,7 +4206,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -4208,7 +4214,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -4216,7 +4222,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -4224,7 +4230,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -4232,7 +4238,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -4240,7 +4246,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -4248,7 +4254,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -4256,7 +4262,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -4264,7 +4270,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -4272,7 +4278,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -4280,7 +4286,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -4288,7 +4294,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -4296,7 +4302,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -4304,7 +4310,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -4312,7 +4318,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -4320,7 +4326,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -4328,7 +4334,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -4336,7 +4342,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -4344,7 +4350,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -4352,7 +4358,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -4360,7 +4366,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -4368,7 +4374,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -4376,7 +4382,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -4384,7 +4390,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -4392,7 +4398,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -4400,7 +4406,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -4408,7 +4414,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -4416,7 +4422,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -4424,7 +4430,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -4432,7 +4438,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -4440,7 +4446,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -4448,7 +4454,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -4456,7 +4462,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -4464,7 +4470,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -4472,7 +4478,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -4480,7 +4486,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -4488,7 +4494,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -4496,7 +4502,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -4504,7 +4510,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -4512,7 +4518,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -4520,7 +4526,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -4528,7 +4534,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -4536,7 +4542,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -4544,7 +4550,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -4552,7 +4558,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -4560,7 +4566,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -4568,7 +4574,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -4576,7 +4582,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -4584,7 +4590,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -4592,7 +4598,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -4600,7 +4606,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -4608,7 +4614,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -4616,7 +4622,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -4624,7 +4630,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -4632,7 +4638,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -4640,7 +4646,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -4648,7 +4654,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -4656,7 +4662,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -4664,7 +4670,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -4672,7 +4678,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -4680,7 +4686,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -4688,7 +4694,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -4696,7 +4702,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -4704,7 +4710,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -4712,7 +4718,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -4720,7 +4726,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -4728,7 +4734,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -4736,7 +4742,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -4744,7 +4750,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -4752,7 +4758,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -4760,7 +4766,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -4768,7 +4774,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -4776,7 +4782,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -4784,7 +4790,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -4792,7 +4798,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -4800,7 +4806,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -4808,7 +4814,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -4816,7 +4822,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -4824,7 +4830,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -4832,7 +4838,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -4840,7 +4846,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -4848,7 +4854,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -4856,7 +4862,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -4864,7 +4870,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -4872,7 +4878,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -4880,7 +4886,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -4888,7 +4894,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -4896,7 +4902,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -4904,7 +4910,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -4912,7 +4918,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -4920,7 +4926,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -4928,7 +4934,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -4936,7 +4942,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -4944,7 +4950,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -4952,7 +4958,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -4960,7 +4966,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -4968,7 +4974,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -4976,7 +4982,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4984,7 +4990,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4992,7 +4998,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -5000,7 +5006,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -5008,7 +5014,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -5016,7 +5022,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -5024,7 +5030,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -5032,7 +5038,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -5040,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -5048,7 +5054,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -5056,7 +5062,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -5064,7 +5070,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -5072,7 +5078,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -5080,7 +5086,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -5088,7 +5094,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -5096,7 +5102,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -5104,7 +5110,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -5112,7 +5118,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -5120,7 +5126,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -5128,7 +5134,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -5136,7 +5142,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -5144,7 +5150,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -5152,7 +5158,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -5160,7 +5166,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -5168,7 +5174,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
@@ -5176,7 +5182,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
@@ -5184,7 +5190,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
@@ -5192,7 +5198,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -5200,7 +5206,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
@@ -5208,7 +5214,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
@@ -5216,7 +5222,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
@@ -5224,7 +5230,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
@@ -5232,7 +5238,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
@@ -5240,7 +5246,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
@@ -5248,7 +5254,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
@@ -5256,7 +5262,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
@@ -5264,7 +5270,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
@@ -5272,7 +5278,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
@@ -5280,7 +5286,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
@@ -5288,7 +5294,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>715</v>
+        <v>851</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
@@ -5296,7 +5302,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
@@ -5304,7 +5310,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
@@ -5312,7 +5318,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
@@ -5320,7 +5326,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
@@ -5328,7 +5334,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
@@ -5336,7 +5342,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
@@ -5344,7 +5350,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -5352,7 +5358,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -5360,7 +5366,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -5368,7 +5374,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -5376,7 +5382,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -5384,7 +5390,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -5392,7 +5398,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -5400,7 +5406,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -5408,7 +5414,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -5416,7 +5422,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -5424,7 +5430,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -5432,7 +5438,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -5440,7 +5446,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -5448,7 +5454,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -5456,7 +5462,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -5464,7 +5470,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -5472,7 +5478,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -5480,7 +5486,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -5488,7 +5494,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -5496,7 +5502,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -5504,7 +5510,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -5512,7 +5518,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -5520,7 +5526,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -5528,7 +5534,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -5536,7 +5542,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -5544,7 +5550,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -5552,7 +5558,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -5560,7 +5566,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -5568,7 +5574,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -5576,7 +5582,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -5584,7 +5590,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -5592,7 +5598,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -5600,7 +5606,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -5608,7 +5614,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
@@ -5616,7 +5622,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
@@ -5624,7 +5630,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
@@ -5632,7 +5638,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
@@ -5640,7 +5646,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
@@ -5648,7 +5654,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
@@ -5656,7 +5662,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
@@ -5664,7 +5670,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
@@ -5672,7 +5678,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
@@ -5680,7 +5686,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
@@ -5688,7 +5694,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
@@ -5696,7 +5702,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
@@ -5704,7 +5710,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
@@ -5712,7 +5718,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
@@ -5720,7 +5726,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
@@ -5728,7 +5734,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -5736,7 +5742,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
@@ -5744,7 +5750,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
@@ -5752,7 +5758,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
@@ -5760,7 +5766,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
@@ -5768,7 +5774,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
@@ -5776,7 +5782,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
@@ -5784,7 +5790,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
@@ -5792,7 +5798,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
@@ -5800,7 +5806,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
@@ -5808,7 +5814,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
@@ -5816,7 +5822,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
@@ -5824,7 +5830,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
@@ -5832,7 +5838,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
@@ -5840,7 +5846,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
@@ -5848,7 +5854,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
@@ -5856,7 +5862,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -5864,7 +5870,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
@@ -5872,7 +5878,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
@@ -5880,7 +5886,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
@@ -5888,7 +5894,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
@@ -5896,7 +5902,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
@@ -5904,7 +5910,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
@@ -5912,7 +5918,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
@@ -5920,7 +5926,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
@@ -5928,7 +5934,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
@@ -5936,7 +5942,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
@@ -5944,7 +5950,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
@@ -5952,7 +5958,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
@@ -5960,7 +5966,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
@@ -5968,7 +5974,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
@@ -5976,7 +5982,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
@@ -5984,7 +5990,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
@@ -5992,7 +5998,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -6000,7 +6006,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -6008,7 +6014,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
@@ -6016,7 +6022,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
@@ -6024,7 +6030,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -6032,7 +6038,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -6040,7 +6046,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -6048,7 +6054,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -6056,7 +6062,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -6064,7 +6070,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -6072,7 +6078,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -6080,7 +6086,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -6088,7 +6094,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -6096,7 +6102,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -6104,7 +6110,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -6112,7 +6118,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -6120,7 +6126,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -6128,7 +6134,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -6136,7 +6142,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -6144,7 +6150,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -6152,7 +6158,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -6160,7 +6166,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -6168,7 +6174,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -6176,7 +6182,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -6184,7 +6190,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -6192,7 +6198,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -6200,7 +6206,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -6208,7 +6214,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -6216,7 +6222,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -6224,7 +6230,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -6232,7 +6238,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -6240,7 +6246,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -6248,7 +6254,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -6256,7 +6262,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -6264,7 +6270,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -6272,7 +6278,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -6280,7 +6286,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -6288,7 +6294,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -6296,7 +6302,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -6304,7 +6310,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -6312,7 +6318,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -6320,7 +6326,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -6328,7 +6334,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -6336,7 +6342,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
@@ -6344,7 +6350,7 @@
         <v>39994394</v>
       </c>
       <c r="B426" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
@@ -6352,6 +6358,14 @@
         <v>26434505</v>
       </c>
       <c r="B427" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>22997027</v>
+      </c>
+      <c r="B428" t="s">
         <v>850</v>
       </c>
     </row>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\2026-10-22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario Libre\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D36153-0927-445C-A767-CC8BE475DE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{518AEC0D-5448-48DC-85CF-DFEBBB2604A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>DNI</t>
   </si>
@@ -31,7 +44,10 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>GOMEZ MARCELO D.</t>
+    <t>gomez marcelo</t>
+  </si>
+  <si>
+    <t>farinella pedro</t>
   </si>
 </sst>
 </file>
@@ -385,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -407,6 +423,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>21232323</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario Libre\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{518AEC0D-5448-48DC-85CF-DFEBBB2604A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416DD53E-1481-40C5-8C62-F00B6FBE47AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>DNI</t>
   </si>
@@ -44,10 +44,13 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>gomez marcelo</t>
+    <t>FARinela pedro</t>
   </si>
   <si>
-    <t>farinella pedro</t>
+    <t>gomez  MarceLO</t>
+  </si>
+  <si>
+    <t>peralta nistorr</t>
   </si>
 </sst>
 </file>
@@ -401,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -417,7 +420,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>23977476</v>
+        <v>28855943</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -425,10 +428,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>21232323</v>
+        <v>23977476</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>21212121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario Libre\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acreditaciones\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416DD53E-1481-40C5-8C62-F00B6FBE47AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5448"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="880">
   <si>
     <t>DNI</t>
   </si>
@@ -44,19 +43,2644 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>FARinela pedro</t>
-  </si>
-  <si>
-    <t>gomez  MarceLO</t>
-  </si>
-  <si>
-    <t>peralta nistorr</t>
+    <t>29557897</t>
+  </si>
+  <si>
+    <t>GAMERO VILANIS MARIA NOELIA</t>
+  </si>
+  <si>
+    <t>35210165</t>
+  </si>
+  <si>
+    <t>FLORES LUCILA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>22063719</t>
+  </si>
+  <si>
+    <t>BALDIVIESO ALONSO ROLANDO</t>
+  </si>
+  <si>
+    <t>36033398</t>
+  </si>
+  <si>
+    <t>CHAVES CACERES NOELIA PATRICIA</t>
+  </si>
+  <si>
+    <t>29176478</t>
+  </si>
+  <si>
+    <t>ACCORONI LUBER ANDREA GABRIELA</t>
+  </si>
+  <si>
+    <t>29176054</t>
+  </si>
+  <si>
+    <t>PEREZ BEDINI MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>29778440</t>
+  </si>
+  <si>
+    <t>ALANIZ CECILIA VERONICA</t>
+  </si>
+  <si>
+    <t>31812653</t>
+  </si>
+  <si>
+    <t>RUARTE MARIA JOSE</t>
+  </si>
+  <si>
+    <t>30708968</t>
+  </si>
+  <si>
+    <t>COLOMBO MARTIN EXEQUIEL</t>
+  </si>
+  <si>
+    <t>22935616</t>
+  </si>
+  <si>
+    <t>ORTIZ VERONICA SILVINA</t>
+  </si>
+  <si>
+    <t>30768546</t>
+  </si>
+  <si>
+    <t>YANZÓN ELIZABETH LEONOR</t>
+  </si>
+  <si>
+    <t>22438126</t>
+  </si>
+  <si>
+    <t>CASTRACANI SIREROL CLAUDIA MARIELA</t>
+  </si>
+  <si>
+    <t>41957633</t>
+  </si>
+  <si>
+    <t>ADORNO CARRIZO AGUSTINA GUADALUPE</t>
+  </si>
+  <si>
+    <t>26287456</t>
+  </si>
+  <si>
+    <t>CASTRO FLORES EMILCE NOELIA</t>
+  </si>
+  <si>
+    <t>41776139</t>
+  </si>
+  <si>
+    <t>CATALDO DIAZ CARLA NOEMÍ</t>
+  </si>
+  <si>
+    <t>22997803</t>
+  </si>
+  <si>
+    <t>ARAYA ANDREA FABIANA</t>
+  </si>
+  <si>
+    <t>22519441</t>
+  </si>
+  <si>
+    <t>QUIROGA ELENA BEATRIZ</t>
+  </si>
+  <si>
+    <t>33766697</t>
+  </si>
+  <si>
+    <t>NAVAS ECHENIQUE ELIO IVÁN</t>
+  </si>
+  <si>
+    <t>23977509</t>
+  </si>
+  <si>
+    <t>REMENTERIA CLAUDIA ISABEL</t>
+  </si>
+  <si>
+    <t>35192484</t>
+  </si>
+  <si>
+    <t>CORRAL CRUZ DEBORA GABRIELA</t>
+  </si>
+  <si>
+    <t>18795886</t>
+  </si>
+  <si>
+    <t>SEGOVIA MARIA LAURA</t>
+  </si>
+  <si>
+    <t>27784095</t>
+  </si>
+  <si>
+    <t>FUNES SONIA DANIELA</t>
+  </si>
+  <si>
+    <t>29098038</t>
+  </si>
+  <si>
+    <t>LUNA ANIBAL JULIO</t>
+  </si>
+  <si>
+    <t>39011581</t>
+  </si>
+  <si>
+    <t>FRIAS FATIMA CELESTE</t>
+  </si>
+  <si>
+    <t>39182783</t>
+  </si>
+  <si>
+    <t>AVENDAÑO VERA LORENA GISEL</t>
+  </si>
+  <si>
+    <t>34255785</t>
+  </si>
+  <si>
+    <t>GARCIA YESICA EDITH</t>
+  </si>
+  <si>
+    <t>23576120</t>
+  </si>
+  <si>
+    <t>NIEVAS ARACENA BARBARITA DEOLINDA</t>
+  </si>
+  <si>
+    <t>39009938</t>
+  </si>
+  <si>
+    <t>QUIROGA NIEVAS FLORENCIA MARISEL</t>
+  </si>
+  <si>
+    <t>30932955</t>
+  </si>
+  <si>
+    <t>SANCHEZ CELINA ILIANA</t>
+  </si>
+  <si>
+    <t>18512033</t>
+  </si>
+  <si>
+    <t>ROMERO FLAVIO RUBEN</t>
+  </si>
+  <si>
+    <t>26740703</t>
+  </si>
+  <si>
+    <t>PALACIO ANALIA VERONICA</t>
+  </si>
+  <si>
+    <t>27260920</t>
+  </si>
+  <si>
+    <t>MALDONADO MARCELA LORENA</t>
+  </si>
+  <si>
+    <t>21955818</t>
+  </si>
+  <si>
+    <t>FURQUE OMAR LEONARDO</t>
+  </si>
+  <si>
+    <t>31514109</t>
+  </si>
+  <si>
+    <t>PONCE MOLINERO LAURA VALERIA</t>
+  </si>
+  <si>
+    <t>28263330</t>
+  </si>
+  <si>
+    <t>LORENTE NATALIA SILVANA</t>
+  </si>
+  <si>
+    <t>26287553</t>
+  </si>
+  <si>
+    <t>CABALLERO GONZALEZ JOSE EMILIO</t>
+  </si>
+  <si>
+    <t>22997651</t>
+  </si>
+  <si>
+    <t>MARTIN MARIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>23576194</t>
+  </si>
+  <si>
+    <t>SALAS CASTRO ANA CARINA</t>
+  </si>
+  <si>
+    <t>24234970</t>
+  </si>
+  <si>
+    <t>SANTANDREU CELANI MÓNICA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>28475611</t>
+  </si>
+  <si>
+    <t>SAMPER MARIA CRISTINA</t>
+  </si>
+  <si>
+    <t>24234532</t>
+  </si>
+  <si>
+    <t>CORDOBA CLAUDIA CARINA</t>
+  </si>
+  <si>
+    <t>32860358</t>
+  </si>
+  <si>
+    <t>SANCHEZ JOHANA MARIANELA</t>
+  </si>
+  <si>
+    <t>32116552</t>
+  </si>
+  <si>
+    <t>LUNA VANINA GISELLE</t>
+  </si>
+  <si>
+    <t>27916706</t>
+  </si>
+  <si>
+    <t>LOPEZ OSCAR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>24948022</t>
+  </si>
+  <si>
+    <t>SEGOVIA MARCELA DEL VALLE</t>
+  </si>
+  <si>
+    <t>26878735</t>
+  </si>
+  <si>
+    <t>ESCUDERO NATALIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>24331478</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ NORMA BEATRIZ</t>
+  </si>
+  <si>
+    <t>23498141</t>
+  </si>
+  <si>
+    <t>FIGUEROA JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>23567086</t>
+  </si>
+  <si>
+    <t>CORIA AUGUSTO ANDREA LILIANA</t>
+  </si>
+  <si>
+    <t>31401482</t>
+  </si>
+  <si>
+    <t>GOMEZ ANDRES CAYETANO</t>
+  </si>
+  <si>
+    <t>42805589</t>
+  </si>
+  <si>
+    <t>ESPEJO MARIA AYELEN</t>
+  </si>
+  <si>
+    <t>28088836</t>
+  </si>
+  <si>
+    <t>GONZALEZ ROCIO DEL PILAR</t>
+  </si>
+  <si>
+    <t>29481582</t>
+  </si>
+  <si>
+    <t>PUERTAS LOPEZ MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>31633291</t>
+  </si>
+  <si>
+    <t>SANCHEZ ESCAMILLA MIRIAN</t>
+  </si>
+  <si>
+    <t>34698849</t>
+  </si>
+  <si>
+    <t>NORIEGA CAROLINA LAURA</t>
+  </si>
+  <si>
+    <t>29176391</t>
+  </si>
+  <si>
+    <t>LUNA VERA EMELINA SUSANA</t>
+  </si>
+  <si>
+    <t>25573317</t>
+  </si>
+  <si>
+    <t>CORTEZ MERCADO JULIA ELENA</t>
+  </si>
+  <si>
+    <t>34590320</t>
+  </si>
+  <si>
+    <t>PEREIRA ARCE LAURA YESICA</t>
+  </si>
+  <si>
+    <t>29889040</t>
+  </si>
+  <si>
+    <t>PENA CECILIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>31214229</t>
+  </si>
+  <si>
+    <t>RIVEROS ADRIANA ANTONIA</t>
+  </si>
+  <si>
+    <t>32689022</t>
+  </si>
+  <si>
+    <t>SANCHEZ MONTAÑEZ MARIA PAULA</t>
+  </si>
+  <si>
+    <t>23545139</t>
+  </si>
+  <si>
+    <t>PETRIGNANI RIVEROS MARIA VERONICA</t>
+  </si>
+  <si>
+    <t>35334647</t>
+  </si>
+  <si>
+    <t>DI CARLO GONZALEZ GONZALO EZEQUIEL</t>
+  </si>
+  <si>
+    <t>31633022</t>
+  </si>
+  <si>
+    <t>MONTANA CRISTINA VANESA</t>
+  </si>
+  <si>
+    <t>22658634</t>
+  </si>
+  <si>
+    <t>CORZO GRACIELA EDIT</t>
+  </si>
+  <si>
+    <t>25590318</t>
+  </si>
+  <si>
+    <t>GODOY CASTRO LINA FABIANA</t>
+  </si>
+  <si>
+    <t>35849137</t>
+  </si>
+  <si>
+    <t>ALVAREZ FARIAS GISELA JESUS</t>
+  </si>
+  <si>
+    <t>29034892</t>
+  </si>
+  <si>
+    <t>CAROSELLI ALEJANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>22597626</t>
+  </si>
+  <si>
+    <t>FARIAS MUÑOZ GLADYS MIRTHA</t>
+  </si>
+  <si>
+    <t>18542025</t>
+  </si>
+  <si>
+    <t>GODOY DENISE CLORINDA</t>
+  </si>
+  <si>
+    <t>26790041</t>
+  </si>
+  <si>
+    <t>SOTO GALAS MARIA GABRIELA</t>
+  </si>
+  <si>
+    <t>22959865</t>
+  </si>
+  <si>
+    <t>FLORES FABIANA VERONICA</t>
+  </si>
+  <si>
+    <t>35149329</t>
+  </si>
+  <si>
+    <t>CABRERA LANGHI ANA CELESTE</t>
+  </si>
+  <si>
+    <t>27614081</t>
+  </si>
+  <si>
+    <t>YANEZ VALERIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>20344716</t>
+  </si>
+  <si>
+    <t>ROSSELOT SANDRA MABEL</t>
+  </si>
+  <si>
+    <t>21610090</t>
+  </si>
+  <si>
+    <t>GUILLEN BETINA LUCIA</t>
+  </si>
+  <si>
+    <t>30634134</t>
+  </si>
+  <si>
+    <t>GUAJARDO BALMACEDA VANESA ELIZABETH</t>
+  </si>
+  <si>
+    <t>39182884</t>
+  </si>
+  <si>
+    <t>IBANEZ NEHIN MARIA EMILCE</t>
+  </si>
+  <si>
+    <t>35852486</t>
+  </si>
+  <si>
+    <t>GOMEZ VANESA GISEL</t>
+  </si>
+  <si>
+    <t>43376753</t>
+  </si>
+  <si>
+    <t>BARRIONUEVO TAPIA BRISA JAZMIN</t>
+  </si>
+  <si>
+    <t>35505524</t>
+  </si>
+  <si>
+    <t>VELASCO MALBERTI MARIA EMILIA</t>
+  </si>
+  <si>
+    <t>36424280</t>
+  </si>
+  <si>
+    <t>ROSSOMANDO MANCHADO PAOLA ANTONELLA</t>
+  </si>
+  <si>
+    <t>22875791</t>
+  </si>
+  <si>
+    <t>VALDEZ ANA MARIA</t>
+  </si>
+  <si>
+    <t>31125541</t>
+  </si>
+  <si>
+    <t>PAROLDI TATIANA YAEL</t>
+  </si>
+  <si>
+    <t>32689386</t>
+  </si>
+  <si>
+    <t>RAMIREZ FREDES ELISA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>22358316</t>
+  </si>
+  <si>
+    <t>DUARTE ZAPATA PATRICIA IVANA</t>
+  </si>
+  <si>
+    <t>44317127</t>
+  </si>
+  <si>
+    <t>OJEDA GARRAMUO MARIA LUDMILA</t>
+  </si>
+  <si>
+    <t>25118960</t>
+  </si>
+  <si>
+    <t>PEREZ RODRIGO CELINA</t>
+  </si>
+  <si>
+    <t>26434297</t>
+  </si>
+  <si>
+    <t>CUCCA VIVIANA ESTELA</t>
+  </si>
+  <si>
+    <t>28841687</t>
+  </si>
+  <si>
+    <t>AVILA YANINA VALERIA</t>
+  </si>
+  <si>
+    <t>25938967</t>
+  </si>
+  <si>
+    <t>DAVILA NANCY NATALIA</t>
+  </si>
+  <si>
+    <t>32689428</t>
+  </si>
+  <si>
+    <t>MORON GABRIELA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>24480426</t>
+  </si>
+  <si>
+    <t>GOMEZ SONIA FABIANA</t>
+  </si>
+  <si>
+    <t>22065100</t>
+  </si>
+  <si>
+    <t>TEJADA SARA BEATRIZ</t>
+  </si>
+  <si>
+    <t>34698649</t>
+  </si>
+  <si>
+    <t>GARCIA TORRES MARIA JOSE</t>
+  </si>
+  <si>
+    <t>25549818</t>
+  </si>
+  <si>
+    <t>TELLO MARTA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>29889140</t>
+  </si>
+  <si>
+    <t>GONZALEZ GILYAN MARIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>38463696</t>
+  </si>
+  <si>
+    <t>QUIROGA VERON LEONARDO MARTIN</t>
+  </si>
+  <si>
+    <t>34430098</t>
+  </si>
+  <si>
+    <t>LOPARDO JULIETA LARA</t>
+  </si>
+  <si>
+    <t>23313993</t>
+  </si>
+  <si>
+    <t>AVILA GABRIELA ISABEL</t>
+  </si>
+  <si>
+    <t>35848301</t>
+  </si>
+  <si>
+    <t>ASTUDILLO TAMARA PAMELA</t>
+  </si>
+  <si>
+    <t>33321722</t>
+  </si>
+  <si>
+    <t>COLOMBO RODRIGUEZ ESTEFANIA</t>
+  </si>
+  <si>
+    <t>38462016</t>
+  </si>
+  <si>
+    <t>GOMEZ BATTEZZATI AGOSTINA DEL PILAR</t>
+  </si>
+  <si>
+    <t>25938634</t>
+  </si>
+  <si>
+    <t>DE LA TORRE MARTIN MARIA</t>
+  </si>
+  <si>
+    <t>32354359</t>
+  </si>
+  <si>
+    <t>SIMON DESIREE DEL VALLE</t>
+  </si>
+  <si>
+    <t>34047688</t>
+  </si>
+  <si>
+    <t>DONOSO GIMENA</t>
+  </si>
+  <si>
+    <t>23982696</t>
+  </si>
+  <si>
+    <t>FERRER MACIAS MARIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>23378720</t>
+  </si>
+  <si>
+    <t>BRAGAGNOLO STELLA MARYS</t>
+  </si>
+  <si>
+    <t>40591335</t>
+  </si>
+  <si>
+    <t>STABILE GILDA JAZMN</t>
+  </si>
+  <si>
+    <t>24948017</t>
+  </si>
+  <si>
+    <t>SANCHEZ MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>31929750</t>
+  </si>
+  <si>
+    <t>SILVA MALLEA MARIA BELEN</t>
+  </si>
+  <si>
+    <t>41083294</t>
+  </si>
+  <si>
+    <t>MEDRANO JOFRE EMILIANA MACARENA</t>
+  </si>
+  <si>
+    <t>38594910</t>
+  </si>
+  <si>
+    <t>TRIGO YANINA ESTEFANIA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>38463693</t>
+  </si>
+  <si>
+    <t>SAEZ MALLAMACI BRUNO</t>
+  </si>
+  <si>
+    <t>22003602</t>
+  </si>
+  <si>
+    <t>ECHEVARRIA MERCEDES BEATRIZ</t>
+  </si>
+  <si>
+    <t>21359584</t>
+  </si>
+  <si>
+    <t>GARRO MIRIAM RENEE</t>
+  </si>
+  <si>
+    <t>40266078</t>
+  </si>
+  <si>
+    <t>VEGA MELANIE YAMILA</t>
+  </si>
+  <si>
+    <t>24735417</t>
+  </si>
+  <si>
+    <t>URBANO JULIO ANTONIO</t>
+  </si>
+  <si>
+    <t>43489601</t>
+  </si>
+  <si>
+    <t>ROMERO NOELIA MARIBEL</t>
+  </si>
+  <si>
+    <t>23982654</t>
+  </si>
+  <si>
+    <t>GONZALEZ GRACIELA DECIDERIA</t>
+  </si>
+  <si>
+    <t>33117660</t>
+  </si>
+  <si>
+    <t>ZALAZAR CINTIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>22063365</t>
+  </si>
+  <si>
+    <t>SOLIS ROSA BEATRIZ</t>
+  </si>
+  <si>
+    <t>28020998</t>
+  </si>
+  <si>
+    <t>QUINTEROS MARIA CELINA</t>
+  </si>
+  <si>
+    <t>32807801</t>
+  </si>
+  <si>
+    <t>GOMEZ NIGRES PAMELA BEATRIZ</t>
+  </si>
+  <si>
+    <t>27261100</t>
+  </si>
+  <si>
+    <t>PAEZ GLORIA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>25714472</t>
+  </si>
+  <si>
+    <t>LUCERO BRIZUELA ALEJANDRA LIDIA</t>
+  </si>
+  <si>
+    <t>30768543</t>
+  </si>
+  <si>
+    <t>BUSTOS CAROLINA DEL VALLE</t>
+  </si>
+  <si>
+    <t>28243055</t>
+  </si>
+  <si>
+    <t>VAZQUEZ MARINA BEATRIZ</t>
+  </si>
+  <si>
+    <t>28967232</t>
+  </si>
+  <si>
+    <t>ESPINOZA CASTRO LILIANA ELENA</t>
+  </si>
+  <si>
+    <t>31129641</t>
+  </si>
+  <si>
+    <t>MERITELLO MONICA DANIELA</t>
+  </si>
+  <si>
+    <t>22064650</t>
+  </si>
+  <si>
+    <t>SALINAS SILVANA ALICIA</t>
+  </si>
+  <si>
+    <t>35507238</t>
+  </si>
+  <si>
+    <t>FURIO ANTONELA PAOLA</t>
+  </si>
+  <si>
+    <t>30626591</t>
+  </si>
+  <si>
+    <t>IBAÆEZ GABRIELA JESSICA</t>
+  </si>
+  <si>
+    <t>23027947</t>
+  </si>
+  <si>
+    <t>GUIDI VENERDINI MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>38075342</t>
+  </si>
+  <si>
+    <t>GONZALEZ EMILI TAMARA</t>
+  </si>
+  <si>
+    <t>28243469</t>
+  </si>
+  <si>
+    <t>MORALES VANESA ESTELA</t>
+  </si>
+  <si>
+    <t>31372237</t>
+  </si>
+  <si>
+    <t>PONCE FELIPUCHE MARCELA ANALIA</t>
+  </si>
+  <si>
+    <t>31129543</t>
+  </si>
+  <si>
+    <t>OLMEDO GOYOCHEA JOHANA DANIELA</t>
+  </si>
+  <si>
+    <t>24693939</t>
+  </si>
+  <si>
+    <t>CASTRACANI CAROLA ANDREA</t>
+  </si>
+  <si>
+    <t>30243868</t>
+  </si>
+  <si>
+    <t>MORRA PRESNO ROBERTO JAVIER</t>
+  </si>
+  <si>
+    <t>37531215</t>
+  </si>
+  <si>
+    <t>ROMERO ALVARADO MARIANO ABEL</t>
+  </si>
+  <si>
+    <t>21955746</t>
+  </si>
+  <si>
+    <t>ORO YOLANDA BEATRIZ</t>
+  </si>
+  <si>
+    <t>28726347</t>
+  </si>
+  <si>
+    <t>NAVEDA MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>38216143</t>
+  </si>
+  <si>
+    <t>GUEVARA GAITAN KARINA MICAELA</t>
+  </si>
+  <si>
+    <t>22291766</t>
+  </si>
+  <si>
+    <t>CALLEJA LAURA SILVANA</t>
+  </si>
+  <si>
+    <t>24526494</t>
+  </si>
+  <si>
+    <t>SOLIS CAROLINA ROSANA</t>
+  </si>
+  <si>
+    <t>35923242</t>
+  </si>
+  <si>
+    <t>ROSALES SAAVEDRA KARINA BELEN</t>
+  </si>
+  <si>
+    <t>32447643</t>
+  </si>
+  <si>
+    <t>DONOSO MYRIAM BEATRIZ</t>
+  </si>
+  <si>
+    <t>24464052</t>
+  </si>
+  <si>
+    <t>PERRONE PAEZ CLAUDIA BERENICE</t>
+  </si>
+  <si>
+    <t>31005506</t>
+  </si>
+  <si>
+    <t>CORZO NOELIA NOEMI</t>
+  </si>
+  <si>
+    <t>22358379</t>
+  </si>
+  <si>
+    <t>ORTIZ PATRICIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>24168512</t>
+  </si>
+  <si>
+    <t>CARABAJAL MARIA ADELINA</t>
+  </si>
+  <si>
+    <t>35540958</t>
+  </si>
+  <si>
+    <t>RAMOS CAMACHO SAMUEL EXEQUIEL</t>
+  </si>
+  <si>
+    <t>22774488</t>
+  </si>
+  <si>
+    <t>D. VIRGILIO MARIA DANIELA</t>
+  </si>
+  <si>
+    <t>35509364</t>
+  </si>
+  <si>
+    <t>CASTRO MOLINA ELIANA GISELLE</t>
+  </si>
+  <si>
+    <t>24038971</t>
+  </si>
+  <si>
+    <t>PAEZ GRACIELA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>33766633</t>
+  </si>
+  <si>
+    <t>ESPINOSA SEGOVIA PAMELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>31401507</t>
+  </si>
+  <si>
+    <t>ALVAREZ ANA MARIA</t>
+  </si>
+  <si>
+    <t>34916649</t>
+  </si>
+  <si>
+    <t>GUZMAN MAYRA JOHANA</t>
+  </si>
+  <si>
+    <t>29507930</t>
+  </si>
+  <si>
+    <t>PAEZ PAOLA MABEL</t>
+  </si>
+  <si>
+    <t>32860072</t>
+  </si>
+  <si>
+    <t>GOMEZ COLOMA VIRGINIA</t>
+  </si>
+  <si>
+    <t>38591484</t>
+  </si>
+  <si>
+    <t>MERCADO VANINA DANIELA</t>
+  </si>
+  <si>
+    <t>28967984</t>
+  </si>
+  <si>
+    <t>ALCANTARO ROSA PAOLA</t>
+  </si>
+  <si>
+    <t>25786427</t>
+  </si>
+  <si>
+    <t>D'ANGELO VANESSA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>22998994</t>
+  </si>
+  <si>
+    <t>PEREZ IVANA VERONICA</t>
+  </si>
+  <si>
+    <t>20275847</t>
+  </si>
+  <si>
+    <t>MORALES RICARDO MARCELO</t>
+  </si>
+  <si>
+    <t>41054009</t>
+  </si>
+  <si>
+    <t>FLORES FLORES PRISCILA TAMARA</t>
+  </si>
+  <si>
+    <t>28698273</t>
+  </si>
+  <si>
+    <t>HOMES ANALIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>36254114</t>
+  </si>
+  <si>
+    <t>BAZAN MORLAS JIMENA ANABEL</t>
+  </si>
+  <si>
+    <t>44316665</t>
+  </si>
+  <si>
+    <t>BALMACEDA GOMEZ TAMARA NATALI</t>
+  </si>
+  <si>
+    <t>37297759</t>
+  </si>
+  <si>
+    <t>MELIAN MARIANA</t>
+  </si>
+  <si>
+    <t>35735583</t>
+  </si>
+  <si>
+    <t>ORTEGA YACANTO JOHANA BELEN</t>
+  </si>
+  <si>
+    <t>23189759</t>
+  </si>
+  <si>
+    <t>SANCHEZ MONICA VIVIANA</t>
+  </si>
+  <si>
+    <t>33585145</t>
+  </si>
+  <si>
+    <t>MUÑOZ JOFRE ERICA PATRICIA</t>
+  </si>
+  <si>
+    <t>26510007</t>
+  </si>
+  <si>
+    <t>CARDOZO CLAUDIO JAVIER</t>
+  </si>
+  <si>
+    <t>21361540</t>
+  </si>
+  <si>
+    <t>TEJADA PATRICIA ROSANA</t>
+  </si>
+  <si>
+    <t>22107306</t>
+  </si>
+  <si>
+    <t>CASTRO ANALIA GRACIELA</t>
+  </si>
+  <si>
+    <t>45264486</t>
+  </si>
+  <si>
+    <t>AGÜERO FABRICIO GABRIEL</t>
+  </si>
+  <si>
+    <t>27784046</t>
+  </si>
+  <si>
+    <t>MERCADO HEBER EDGAR</t>
+  </si>
+  <si>
+    <t>24972343</t>
+  </si>
+  <si>
+    <t>SOSA NATALIA VANESA</t>
+  </si>
+  <si>
+    <t>38076859</t>
+  </si>
+  <si>
+    <t>ALANIZ ROCIO MAGALI</t>
+  </si>
+  <si>
+    <t>24020387</t>
+  </si>
+  <si>
+    <t>ALANIZ MARTA CESILIA</t>
+  </si>
+  <si>
+    <t>39425333</t>
+  </si>
+  <si>
+    <t>HERRERA LUCILA VIRGINIA EDITH</t>
+  </si>
+  <si>
+    <t>37317352</t>
+  </si>
+  <si>
+    <t>ALCUCERO MARIA BELEN</t>
+  </si>
+  <si>
+    <t>32624526</t>
+  </si>
+  <si>
+    <t>GONZALEZ SALINAS ANTONIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>35023667</t>
+  </si>
+  <si>
+    <t>GAMBA SEGOVIA OSCAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>21360534</t>
+  </si>
+  <si>
+    <t>RIMOLO SANDRA JUANA</t>
+  </si>
+  <si>
+    <t>24087598</t>
+  </si>
+  <si>
+    <t>RUIZ RIVEROS ANA MARIA</t>
+  </si>
+  <si>
+    <t>21361896</t>
+  </si>
+  <si>
+    <t>PAEZ CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>26790662</t>
+  </si>
+  <si>
+    <t>CASTRO ERICA VANESA</t>
+  </si>
+  <si>
+    <t>29758069</t>
+  </si>
+  <si>
+    <t>ALAMINO ANALI CELESTE SOLEDAD</t>
+  </si>
+  <si>
+    <t>25167834</t>
+  </si>
+  <si>
+    <t>TURELL CARRIZO ANA MARIA</t>
+  </si>
+  <si>
+    <t>24948044</t>
+  </si>
+  <si>
+    <t>ILLANES GEMA ELENA</t>
+  </si>
+  <si>
+    <t>29058219</t>
+  </si>
+  <si>
+    <t>MARTINEZ CECILIA BELEN</t>
+  </si>
+  <si>
+    <t>21935770</t>
+  </si>
+  <si>
+    <t>GUTIERREZ MARIO LUIS</t>
+  </si>
+  <si>
+    <t>26547884</t>
+  </si>
+  <si>
+    <t>VIVARES ROSANA NOELIA</t>
+  </si>
+  <si>
+    <t>22358371</t>
+  </si>
+  <si>
+    <t>ATAMPIZ ROSANA CAROLINA</t>
+  </si>
+  <si>
+    <t>29302836</t>
+  </si>
+  <si>
+    <t>FLORES FLAVIA LILIANA</t>
+  </si>
+  <si>
+    <t>32807934</t>
+  </si>
+  <si>
+    <t>ARROYO ELBA MABEL</t>
+  </si>
+  <si>
+    <t>22003316</t>
+  </si>
+  <si>
+    <t>POBLETE NIEVES MABEL</t>
+  </si>
+  <si>
+    <t>31979400</t>
+  </si>
+  <si>
+    <t>TEJADA FALCON MIRTHA JOHANA</t>
+  </si>
+  <si>
+    <t>24948340</t>
+  </si>
+  <si>
+    <t>ESCOBAR CARINA ISABEL</t>
+  </si>
+  <si>
+    <t>25235267</t>
+  </si>
+  <si>
+    <t>ZEPEDA SILVANA ANDREA</t>
+  </si>
+  <si>
+    <t>34193964</t>
+  </si>
+  <si>
+    <t>VALENZUELA ORO MARIA FLORENCIA</t>
+  </si>
+  <si>
+    <t>26790199</t>
+  </si>
+  <si>
+    <t>BLANC RODRIGUEZ CARLA YANINA</t>
+  </si>
+  <si>
+    <t>23380022</t>
+  </si>
+  <si>
+    <t>RETA PATRICIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>35318083</t>
+  </si>
+  <si>
+    <t>DEL CID LIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>24331464</t>
+  </si>
+  <si>
+    <t>TORRES LORENA EVANGELINA</t>
+  </si>
+  <si>
+    <t>27764037</t>
+  </si>
+  <si>
+    <t>SIGAMPA VANESA MARISOL</t>
+  </si>
+  <si>
+    <t>27350109</t>
+  </si>
+  <si>
+    <t>ROBLEDO ANA PATRICIA</t>
+  </si>
+  <si>
+    <t>32454568</t>
+  </si>
+  <si>
+    <t>CORREA MARIA BELEN</t>
+  </si>
+  <si>
+    <t>34920563</t>
+  </si>
+  <si>
+    <t>BUSTOS CELINA PAOLA</t>
+  </si>
+  <si>
+    <t>28836369</t>
+  </si>
+  <si>
+    <t>CASANOVA NATALIA VANESA</t>
+  </si>
+  <si>
+    <t>37462202</t>
+  </si>
+  <si>
+    <t>PARATORE PAULA GIMENA</t>
+  </si>
+  <si>
+    <t>31044010</t>
+  </si>
+  <si>
+    <t>FLORES MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>35851429</t>
+  </si>
+  <si>
+    <t>AHUMADA ORTIZ JAQUELINE ANDREA</t>
+  </si>
+  <si>
+    <t>26288973</t>
+  </si>
+  <si>
+    <t>LUNA NIDIA VERÔNICA</t>
+  </si>
+  <si>
+    <t>26831361</t>
+  </si>
+  <si>
+    <t>FLORES PATRICIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>22403163</t>
+  </si>
+  <si>
+    <t>GONZALEZ CLAUDIA ANDREA</t>
+  </si>
+  <si>
+    <t>25118938</t>
+  </si>
+  <si>
+    <t>DELGADO IVAN MARCELO</t>
+  </si>
+  <si>
+    <t>25252982</t>
+  </si>
+  <si>
+    <t>LLOPIS PENNATE LAURA BEATRIZ</t>
+  </si>
+  <si>
+    <t>30631066</t>
+  </si>
+  <si>
+    <t>CORDOBA GARAY MARIA INES</t>
+  </si>
+  <si>
+    <t>17120081</t>
+  </si>
+  <si>
+    <t>ROCHA NORMA VIVIANA</t>
+  </si>
+  <si>
+    <t>29264277</t>
+  </si>
+  <si>
+    <t>PALACIO DANIELA ELIANA</t>
+  </si>
+  <si>
+    <t>25649306</t>
+  </si>
+  <si>
+    <t>CABRERA CARINA ANDREA</t>
+  </si>
+  <si>
+    <t>33715091</t>
+  </si>
+  <si>
+    <t>ILLANEZ EDUARDO IGNACIO</t>
+  </si>
+  <si>
+    <t>28720656</t>
+  </si>
+  <si>
+    <t>HASCHER VALERIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>28720883</t>
+  </si>
+  <si>
+    <t>VARAS  LORENA</t>
+  </si>
+  <si>
+    <t>29351761</t>
+  </si>
+  <si>
+    <t>MIRANDA DAVILA NATALIA EDITH</t>
+  </si>
+  <si>
+    <t>40469608</t>
+  </si>
+  <si>
+    <t>CARRIZO ARACENA MARIA ALDANA</t>
+  </si>
+  <si>
+    <t>26288232</t>
+  </si>
+  <si>
+    <t>ESPEJO PATRICIA MABEL</t>
+  </si>
+  <si>
+    <t>27261140</t>
+  </si>
+  <si>
+    <t>PEREZ TELLO IVANA DEL VALLE</t>
+  </si>
+  <si>
+    <t>29889022</t>
+  </si>
+  <si>
+    <t>ROSALES LORENA ELIZABETH</t>
+  </si>
+  <si>
+    <t>27424825</t>
+  </si>
+  <si>
+    <t>PAROLDI DEBORA</t>
+  </si>
+  <si>
+    <t>37833233</t>
+  </si>
+  <si>
+    <t>CLEVERS MARTINA SOFIA</t>
+  </si>
+  <si>
+    <t>38015916</t>
+  </si>
+  <si>
+    <t>VARELA FIGUEROA CAREN ALESANDRA</t>
+  </si>
+  <si>
+    <t>35509126</t>
+  </si>
+  <si>
+    <t>TEJADA FONZALIDA MICAELA ANAHI</t>
+  </si>
+  <si>
+    <t>36034140</t>
+  </si>
+  <si>
+    <t>MORETA NAIR MARIANELA</t>
+  </si>
+  <si>
+    <t>21357706</t>
+  </si>
+  <si>
+    <t>GAY MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>23381088</t>
+  </si>
+  <si>
+    <t>CASTRO CARINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>24091788</t>
+  </si>
+  <si>
+    <t>MUNOZ GABRIELA ELISA</t>
+  </si>
+  <si>
+    <t>27268829</t>
+  </si>
+  <si>
+    <t>ANDAN VIVIANA PAOLA</t>
+  </si>
+  <si>
+    <t>28773601</t>
+  </si>
+  <si>
+    <t>BECERRA CORREA MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t>22741180</t>
+  </si>
+  <si>
+    <t>GUERRERO SILVANA MONICA</t>
+  </si>
+  <si>
+    <t>32693381</t>
+  </si>
+  <si>
+    <t>LUNA DAHIANA VERNICA</t>
+  </si>
+  <si>
+    <t>28444448</t>
+  </si>
+  <si>
+    <t>VERA KARINA BEATRIZ</t>
+  </si>
+  <si>
+    <t>24948239</t>
+  </si>
+  <si>
+    <t>ASTUDILLO CARINA LORENA</t>
+  </si>
+  <si>
+    <t>39299871</t>
+  </si>
+  <si>
+    <t>AVILA HILDA YOLANDA</t>
+  </si>
+  <si>
+    <t>41531659</t>
+  </si>
+  <si>
+    <t>LIMA ANALIA CARLOTA JUANA</t>
+  </si>
+  <si>
+    <t>24879776</t>
+  </si>
+  <si>
+    <t>NUÑEZ CARINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>38464000</t>
+  </si>
+  <si>
+    <t>SANCHEZ INOJOSA MARIANELA DEL VALLE</t>
+  </si>
+  <si>
+    <t>31612151</t>
+  </si>
+  <si>
+    <t>TORRES VALERIA VIRGINIA</t>
+  </si>
+  <si>
+    <t>22997265</t>
+  </si>
+  <si>
+    <t>LUNA LEPEZ ROSANA</t>
+  </si>
+  <si>
+    <t>31869190</t>
+  </si>
+  <si>
+    <t>PONCE ZAIDA JOHANA</t>
+  </si>
+  <si>
+    <t>32007429</t>
+  </si>
+  <si>
+    <t>MOLINA ATENCIO VERONICA NOELIA</t>
+  </si>
+  <si>
+    <t>27574134</t>
+  </si>
+  <si>
+    <t>GELVEZ MARTA ROSANA</t>
+  </si>
+  <si>
+    <t>34054299</t>
+  </si>
+  <si>
+    <t>MARTI GAMEZ RUBEN GABRIEL</t>
+  </si>
+  <si>
+    <t>24266892</t>
+  </si>
+  <si>
+    <t>BUSTOS RECABARREN MARIELA FERNANDA</t>
+  </si>
+  <si>
+    <t>24038054</t>
+  </si>
+  <si>
+    <t>GONZALEZ SILVANA ELENA</t>
+  </si>
+  <si>
+    <t>28357401</t>
+  </si>
+  <si>
+    <t>ALLENDES PATRICIA SUSANA</t>
+  </si>
+  <si>
+    <t>28691512</t>
+  </si>
+  <si>
+    <t>ONTIVEROS NATALIA LORENA</t>
+  </si>
+  <si>
+    <t>22159164</t>
+  </si>
+  <si>
+    <t>ROJAS ALEJANDRA VIVIANA</t>
+  </si>
+  <si>
+    <t>25939866</t>
+  </si>
+  <si>
+    <t>MARCOS ERICA VALERIA</t>
+  </si>
+  <si>
+    <t>32689387</t>
+  </si>
+  <si>
+    <t>RAMIREZ FREDES ANA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>29481420</t>
+  </si>
+  <si>
+    <t>BAZAN MARGARITA ROSANA</t>
+  </si>
+  <si>
+    <t>32938114</t>
+  </si>
+  <si>
+    <t>VILLAFAÑE YOHANA SOLEDAD</t>
+  </si>
+  <si>
+    <t>39954564</t>
+  </si>
+  <si>
+    <t>ALMEIDA RADICETTI AYELEN NOEMI</t>
+  </si>
+  <si>
+    <t>34111462</t>
+  </si>
+  <si>
+    <t>ROJAS YOLANDA ANDREA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>22658635</t>
+  </si>
+  <si>
+    <t>VIDELA MIRTA ROSANA</t>
+  </si>
+  <si>
+    <t>40368871</t>
+  </si>
+  <si>
+    <t>PRADO VALVERDE KARINA NATALIA</t>
+  </si>
+  <si>
+    <t>42356896</t>
+  </si>
+  <si>
+    <t>QUINTERO MILAGROS TAMARA</t>
+  </si>
+  <si>
+    <t>28243919</t>
+  </si>
+  <si>
+    <t>ANDAN SILVINA VANESA</t>
+  </si>
+  <si>
+    <t>29264972</t>
+  </si>
+  <si>
+    <t>PONCE FELIPUCHE CRISTINA NATALIA</t>
+  </si>
+  <si>
+    <t>29960150</t>
+  </si>
+  <si>
+    <t>ACOSTA HEREDIA YANINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>25938062</t>
+  </si>
+  <si>
+    <t>ESPINOSA GARBO CECILIA CELINA</t>
+  </si>
+  <si>
+    <t>37924686</t>
+  </si>
+  <si>
+    <t>CANO FERNANDA GABRIELA</t>
+  </si>
+  <si>
+    <t>40469641</t>
+  </si>
+  <si>
+    <t>FLORES CASTRO ROMINA BEATRZ</t>
+  </si>
+  <si>
+    <t>39920089</t>
+  </si>
+  <si>
+    <t>RIVERO SOFIA DANIELA</t>
+  </si>
+  <si>
+    <t>33542493</t>
+  </si>
+  <si>
+    <t>OLIVERA GISELA ROMINA</t>
+  </si>
+  <si>
+    <t>38460584</t>
+  </si>
+  <si>
+    <t>RUL EVELIN DAYANA</t>
+  </si>
+  <si>
+    <t>41909067</t>
+  </si>
+  <si>
+    <t>FERNANDEZ ROLDAN WALTER ESEQUIEL</t>
+  </si>
+  <si>
+    <t>32140317</t>
+  </si>
+  <si>
+    <t>VEGA CASTILLA VANINA NOELIA</t>
+  </si>
+  <si>
+    <t>22997027</t>
+  </si>
+  <si>
+    <t>URICHE MARCELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>26790203</t>
+  </si>
+  <si>
+    <t>MONTERO ZAPATA ROSANA MARCELA</t>
+  </si>
+  <si>
+    <t>26791092</t>
+  </si>
+  <si>
+    <t>MARTINEZ LUCIA GABRIELA</t>
+  </si>
+  <si>
+    <t>23977864</t>
+  </si>
+  <si>
+    <t>BUSTOS ANA MARIA</t>
+  </si>
+  <si>
+    <t>24480179</t>
+  </si>
+  <si>
+    <t>GATICA MARIA JOSE</t>
+  </si>
+  <si>
+    <t>22997906</t>
+  </si>
+  <si>
+    <t>DURAN CLAUDIA VERANICA</t>
+  </si>
+  <si>
+    <t>36250401</t>
+  </si>
+  <si>
+    <t>ALMARCHA GONZALEZ YANELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>34861374</t>
+  </si>
+  <si>
+    <t>PINTO GARCIA MARCELA INES</t>
+  </si>
+  <si>
+    <t>22327877</t>
+  </si>
+  <si>
+    <t>FIGUEROA NATALIA MARCELA</t>
+  </si>
+  <si>
+    <t>35508209</t>
+  </si>
+  <si>
+    <t>TREO LUCIANA AGOSTINA</t>
+  </si>
+  <si>
+    <t>30631277</t>
+  </si>
+  <si>
+    <t>LEON MARIA CELESTE</t>
+  </si>
+  <si>
+    <t>28538554</t>
+  </si>
+  <si>
+    <t>FIGUEROA MARIA MARTA DEL VALLE</t>
+  </si>
+  <si>
+    <t>42858441</t>
+  </si>
+  <si>
+    <t>CASIVAR CARLA MARIANA</t>
+  </si>
+  <si>
+    <t>36377307</t>
+  </si>
+  <si>
+    <t>QUILPATAY ROSAURA DESIDERIA</t>
+  </si>
+  <si>
+    <t>24836599</t>
+  </si>
+  <si>
+    <t>VALDEZ VANESA MARIA</t>
+  </si>
+  <si>
+    <t>38075570</t>
+  </si>
+  <si>
+    <t>RAMIREZ GUTIERREZ KATIA AIDA</t>
+  </si>
+  <si>
+    <t>35153426</t>
+  </si>
+  <si>
+    <t>OSSA FEDERICO ANA VICTORIA</t>
+  </si>
+  <si>
+    <t>30892789</t>
+  </si>
+  <si>
+    <t>GONZALEZ ALANIZ GRACIELA SOLEDAD</t>
+  </si>
+  <si>
+    <t>32761901</t>
+  </si>
+  <si>
+    <t>GARCIA YAÑEZ MARCELA BEATRIZ</t>
+  </si>
+  <si>
+    <t>27527938</t>
+  </si>
+  <si>
+    <t>TEJADA SILVINA NOELIA</t>
+  </si>
+  <si>
+    <t>41641380</t>
+  </si>
+  <si>
+    <t>GUZMAN ROCIO</t>
+  </si>
+  <si>
+    <t>28727916</t>
+  </si>
+  <si>
+    <t>GONZALEZ VERONICA GEMA</t>
+  </si>
+  <si>
+    <t>30207271</t>
+  </si>
+  <si>
+    <t>BARBOZA EMILIA YOLANDA</t>
+  </si>
+  <si>
+    <t>35852445</t>
+  </si>
+  <si>
+    <t>PAZ ANDINO ELSA MARIANA</t>
+  </si>
+  <si>
+    <t>33166539</t>
+  </si>
+  <si>
+    <t>GODOY ROXANA ANALIA</t>
+  </si>
+  <si>
+    <t>29174766</t>
+  </si>
+  <si>
+    <t>MUÆOZ IVANA PATRICIA</t>
+  </si>
+  <si>
+    <t>33591885</t>
+  </si>
+  <si>
+    <t>FLORES LINARES JOSE LUIS EMILIANO</t>
+  </si>
+  <si>
+    <t>30145582</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ MARTINEZ JESICA MARISEL</t>
+  </si>
+  <si>
+    <t>27574468</t>
+  </si>
+  <si>
+    <t>ABREGO MARIA GABRIELA</t>
+  </si>
+  <si>
+    <t>33836577</t>
+  </si>
+  <si>
+    <t>MAGGIO ROSTOLL MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>41321909</t>
+  </si>
+  <si>
+    <t>JOFRE OTAROLA NAZARENO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>30920272</t>
+  </si>
+  <si>
+    <t>BRIZUELA MARIANELA MARTA</t>
+  </si>
+  <si>
+    <t>26441626</t>
+  </si>
+  <si>
+    <t>BALMACEDA VIVIANA MARIA</t>
+  </si>
+  <si>
+    <t>31005291</t>
+  </si>
+  <si>
+    <t>TULA ELSA LIDIA</t>
+  </si>
+  <si>
+    <t>33460611</t>
+  </si>
+  <si>
+    <t>CAMPOS MARIÑO JESICA NATALIA</t>
+  </si>
+  <si>
+    <t>22227370</t>
+  </si>
+  <si>
+    <t>TIZERA MARIA VANESA</t>
+  </si>
+  <si>
+    <t>32938192</t>
+  </si>
+  <si>
+    <t>ESCUDERO BORBORE SILVANA BELEN</t>
+  </si>
+  <si>
+    <t>26399600</t>
+  </si>
+  <si>
+    <t>LADINO NATALIA CAROLINA</t>
+  </si>
+  <si>
+    <t>34918277</t>
+  </si>
+  <si>
+    <t>VARGAS MAIRA YANINA</t>
+  </si>
+  <si>
+    <t>34062332</t>
+  </si>
+  <si>
+    <t>PEREZ HECTOR JESUS</t>
+  </si>
+  <si>
+    <t>32878003</t>
+  </si>
+  <si>
+    <t>PAEZ ELIANA GISELA</t>
+  </si>
+  <si>
+    <t>24685334</t>
+  </si>
+  <si>
+    <t>VAN DER HORST SILVINA NOEMI</t>
+  </si>
+  <si>
+    <t>25714406</t>
+  </si>
+  <si>
+    <t>ACIAR FERNANDA NOELIA</t>
+  </si>
+  <si>
+    <t>31183495</t>
+  </si>
+  <si>
+    <t>MIRANDA ANA ROSANA</t>
+  </si>
+  <si>
+    <t>41054689</t>
+  </si>
+  <si>
+    <t>CRAVERO GIMENEZ SOFIA DANIELA</t>
+  </si>
+  <si>
+    <t>30768369</t>
+  </si>
+  <si>
+    <t>TORRES VALERIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>32374889</t>
+  </si>
+  <si>
+    <t>VILLENA NOGUERA IVANA ELENA</t>
+  </si>
+  <si>
+    <t>22394173</t>
+  </si>
+  <si>
+    <t>AG£ERO MARIELA INËS</t>
+  </si>
+  <si>
+    <t>24735473</t>
+  </si>
+  <si>
+    <t>ABILA PATRICIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>29621468</t>
+  </si>
+  <si>
+    <t>ZAPATA PAULA CECILIA</t>
+  </si>
+  <si>
+    <t>36687700</t>
+  </si>
+  <si>
+    <t>MORETTI ANALIA CECILIA</t>
+  </si>
+  <si>
+    <t>28376681</t>
+  </si>
+  <si>
+    <t>CARRIZO CARLA VIVIANA</t>
+  </si>
+  <si>
+    <t>26629513</t>
+  </si>
+  <si>
+    <t>ROMERO GUERRERO LAURA ELISABET DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>22003434</t>
+  </si>
+  <si>
+    <t>MOLINA MARISA ISABEL</t>
+  </si>
+  <si>
+    <t>29481342</t>
+  </si>
+  <si>
+    <t>LISI MELISA SORAYA</t>
+  </si>
+  <si>
+    <t>29889038</t>
+  </si>
+  <si>
+    <t>GONZALEZ PONTORIERO CECILIA BETIANA</t>
+  </si>
+  <si>
+    <t>33542391</t>
+  </si>
+  <si>
+    <t>BERTOL MANRIQUE CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>23977768</t>
+  </si>
+  <si>
+    <t>ALONSO MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>28040440</t>
+  </si>
+  <si>
+    <t>CASTRO BALMACEDA CELIA CAROLINA</t>
+  </si>
+  <si>
+    <t>38077507</t>
+  </si>
+  <si>
+    <t>MUOZ VELAZQUEZ MARISOL ALEJANDRA</t>
+  </si>
+  <si>
+    <t>29996963</t>
+  </si>
+  <si>
+    <t>PEDROL CAROLINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>37742342</t>
+  </si>
+  <si>
+    <t>VARAS GOMEZ MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t>38075082</t>
+  </si>
+  <si>
+    <t>MORAN CORREA ANISA BEATRIZ</t>
+  </si>
+  <si>
+    <t>22788303</t>
+  </si>
+  <si>
+    <t>MARTIN DELIA BARBARA</t>
+  </si>
+  <si>
+    <t>29512108</t>
+  </si>
+  <si>
+    <t>BOLADO VALERIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>21358078</t>
+  </si>
+  <si>
+    <t>TOLOMEO MARIA SILVINA</t>
+  </si>
+  <si>
+    <t>39792828</t>
+  </si>
+  <si>
+    <t>CABRERA TRIGO MICAELA AYELEN</t>
+  </si>
+  <si>
+    <t>31870998</t>
+  </si>
+  <si>
+    <t>MANRIQUE PABLO DAVID</t>
+  </si>
+  <si>
+    <t>34328943</t>
+  </si>
+  <si>
+    <t>VERA MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>38462967</t>
+  </si>
+  <si>
+    <t>ASENCIO MICAELA KAREN RITA</t>
+  </si>
+  <si>
+    <t>22753593</t>
+  </si>
+  <si>
+    <t>ORIHUELA MARIELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>27030375</t>
+  </si>
+  <si>
+    <t>ALÉ FLAVIA BELÉN VALERIA</t>
+  </si>
+  <si>
+    <t>27527828</t>
+  </si>
+  <si>
+    <t>OVIEDO MARÌA GEMA</t>
+  </si>
+  <si>
+    <t>31812750</t>
+  </si>
+  <si>
+    <t>AVILA ENRIQUE GASTON</t>
+  </si>
+  <si>
+    <t>35852166</t>
+  </si>
+  <si>
+    <t>CABRERA LANGHI NATALIA ROMINA</t>
+  </si>
+  <si>
+    <t>40728333</t>
+  </si>
+  <si>
+    <t>TALQUENCA VEGA ANDREA PAULA</t>
+  </si>
+  <si>
+    <t>31129932</t>
+  </si>
+  <si>
+    <t>MARATTA AMARFIL LUCIANA BELEN</t>
+  </si>
+  <si>
+    <t>42163764</t>
+  </si>
+  <si>
+    <t>GUEVARA AXEL LEONEL</t>
+  </si>
+  <si>
+    <t>27406797</t>
+  </si>
+  <si>
+    <t>MOREIRA OLGA ELIZABET</t>
+  </si>
+  <si>
+    <t>33058726</t>
+  </si>
+  <si>
+    <t>VILDOZO CARINA JOHANA</t>
+  </si>
+  <si>
+    <t>24948792</t>
+  </si>
+  <si>
+    <t>LACIAR JAVIER ALBERTO</t>
+  </si>
+  <si>
+    <t>31129536</t>
+  </si>
+  <si>
+    <t>CARROZZO FLORES MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>41468942</t>
+  </si>
+  <si>
+    <t>TORRES CARDOZO BRISA AILEN</t>
+  </si>
+  <si>
+    <t>28143010</t>
+  </si>
+  <si>
+    <t>SUAREZ MARIA BELEN</t>
+  </si>
+  <si>
+    <t>39525374</t>
+  </si>
+  <si>
+    <t>PASTEN EVELYN LUCIA</t>
+  </si>
+  <si>
+    <t>20942251</t>
+  </si>
+  <si>
+    <t>CORADO ALEJANDRA LILIAN</t>
+  </si>
+  <si>
+    <t>33793757</t>
+  </si>
+  <si>
+    <t>HUERTA GISELE DORA</t>
+  </si>
+  <si>
+    <t>32860471</t>
+  </si>
+  <si>
+    <t>FLORES ESTELA EUNICE</t>
+  </si>
+  <si>
+    <t>36034208</t>
+  </si>
+  <si>
+    <t>NAVARRETE JUANA ANA NOEMI</t>
+  </si>
+  <si>
+    <t>24362230</t>
+  </si>
+  <si>
+    <t>MIRANDA LUCIA EDITH</t>
+  </si>
+  <si>
+    <t>24244588</t>
+  </si>
+  <si>
+    <t>GOMEZ MARCELA MONICA</t>
+  </si>
+  <si>
+    <t>24301776</t>
+  </si>
+  <si>
+    <t>OVIEDO SILVIA ADRIANA</t>
+  </si>
+  <si>
+    <t>39995825</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ TAPIA KATHERINA AYELEN</t>
+  </si>
+  <si>
+    <t>34920250</t>
+  </si>
+  <si>
+    <t>AG£ERO MELISA VICTORIA</t>
+  </si>
+  <si>
+    <t>25938076</t>
+  </si>
+  <si>
+    <t>ZARATE ANDREA MARCELA</t>
+  </si>
+  <si>
+    <t>39652634</t>
+  </si>
+  <si>
+    <t>DIAZ RIVEROS LEILA AGUSTINA</t>
+  </si>
+  <si>
+    <t>26717736</t>
+  </si>
+  <si>
+    <t>LOPEZ PAULINA ISABEL</t>
+  </si>
+  <si>
+    <t>34921414</t>
+  </si>
+  <si>
+    <t>BAZAN CUELLO FERNANDO ARIEL</t>
+  </si>
+  <si>
+    <t>24480148</t>
+  </si>
+  <si>
+    <t>PONCE SELVA LORENA</t>
+  </si>
+  <si>
+    <t>34875969</t>
+  </si>
+  <si>
+    <t>DE NARDO GINA ORNELLA</t>
+  </si>
+  <si>
+    <t>28218550</t>
+  </si>
+  <si>
+    <t>GONZALEZ LILIANA BEATRIZ</t>
+  </si>
+  <si>
+    <t>33236630</t>
+  </si>
+  <si>
+    <t>ROMERO DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>33460625</t>
+  </si>
+  <si>
+    <t>CANADAS CALIVAR MARCIA ROMINA</t>
+  </si>
+  <si>
+    <t>35508964</t>
+  </si>
+  <si>
+    <t>MARADONA DAYANA SELVA</t>
+  </si>
+  <si>
+    <t>35848287</t>
+  </si>
+  <si>
+    <t>VEDIA MARIANELA JOHANA</t>
+  </si>
+  <si>
+    <t>26434531</t>
+  </si>
+  <si>
+    <t>FERNANDEZ FABIANA VANESA</t>
+  </si>
+  <si>
+    <t>32454349</t>
+  </si>
+  <si>
+    <t>HOGALDE ZUBIETE MARIANA BELEN</t>
+  </si>
+  <si>
+    <t>20935994</t>
+  </si>
+  <si>
+    <t>BUSTOS MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>34195028</t>
+  </si>
+  <si>
+    <t>PASTORIZA CRISTINA VERONICA</t>
+  </si>
+  <si>
+    <t>36586207</t>
+  </si>
+  <si>
+    <t>MARTI GAMEZ SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>18011237</t>
+  </si>
+  <si>
+    <t>SALAS GOMEZ SANDRA ELIZABETH</t>
+  </si>
+  <si>
+    <t>28786225</t>
+  </si>
+  <si>
+    <t>TEJADA DEBORA VALERIA</t>
+  </si>
+  <si>
+    <t>33846154</t>
+  </si>
+  <si>
+    <t>GOMEZ VERONICA VIVIANA</t>
+  </si>
+  <si>
+    <t>31401286</t>
+  </si>
+  <si>
+    <t>VERA MARIA JOSÉ</t>
+  </si>
+  <si>
+    <t>39790589</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ ADRIANA ANGELA GABRIELA</t>
+  </si>
+  <si>
+    <t>24480295</t>
+  </si>
+  <si>
+    <t>BUSTOS PATRICIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>26611330</t>
+  </si>
+  <si>
+    <t>AVILA VERONICA EDITH</t>
+  </si>
+  <si>
+    <t>34062403</t>
+  </si>
+  <si>
+    <t>GUERRA ROMINA VALERIA</t>
+  </si>
+  <si>
+    <t>35510394</t>
+  </si>
+  <si>
+    <t>ZARATE BENEGAS MAYRA JANET</t>
+  </si>
+  <si>
+    <t>33743184</t>
+  </si>
+  <si>
+    <t>ESCODA MARCIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>25937702</t>
+  </si>
+  <si>
+    <t>MARIN VERONICA CECILIA</t>
+  </si>
+  <si>
+    <t>33824661</t>
+  </si>
+  <si>
+    <t>INGLESES VERGARA EMILIO ARIEL</t>
+  </si>
+  <si>
+    <t>40265282</t>
+  </si>
+  <si>
+    <t>BONTEMPO NAZARENA FATIMA</t>
+  </si>
+  <si>
+    <t>34047511</t>
+  </si>
+  <si>
+    <t>BONTEMPO GABRIEL AUGUSTO</t>
+  </si>
+  <si>
+    <t>26434505</t>
+  </si>
+  <si>
+    <t>ANDRADA ZARATE NATALIA GABRIELA</t>
+  </si>
+  <si>
+    <t>25133138</t>
+  </si>
+  <si>
+    <t>GARCIA DIANA</t>
+  </si>
+  <si>
+    <t>35857424</t>
+  </si>
+  <si>
+    <t>BALLESTER LEANDRA EMILCE</t>
+  </si>
+  <si>
+    <t>43078029</t>
+  </si>
+  <si>
+    <t>GONZALEZ CERDERA ROCIO GUADALUPE</t>
+  </si>
+  <si>
+    <t>21610137</t>
+  </si>
+  <si>
+    <t>CORREA CORTS ELSA GABRIELA</t>
+  </si>
+  <si>
+    <t>28888531</t>
+  </si>
+  <si>
+    <t>GARAY MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>39524637</t>
+  </si>
+  <si>
+    <t>GALLARDO MERINO JOHANA MARIANELA</t>
+  </si>
+  <si>
+    <t>26287205</t>
+  </si>
+  <si>
+    <t>BAZAN ROMARION MARIA ELINA</t>
+  </si>
+  <si>
+    <t>30483703</t>
+  </si>
+  <si>
+    <t>ARG£ELLO MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>22003386</t>
+  </si>
+  <si>
+    <t>LEON ANALIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>30568025</t>
+  </si>
+  <si>
+    <t>LARA GABRIELA NATALIA</t>
+  </si>
+  <si>
+    <t>27350544</t>
+  </si>
+  <si>
+    <t>CASTILLO ROSANA FORTUNATA</t>
+  </si>
+  <si>
+    <t>34866684</t>
+  </si>
+  <si>
+    <t>TORRES NAHIR RUBEN NICOLAS</t>
+  </si>
+  <si>
+    <t>20505067</t>
+  </si>
+  <si>
+    <t>LUCERO HILDA CLARISA BETTINA</t>
+  </si>
+  <si>
+    <t>39954625</t>
+  </si>
+  <si>
+    <t>ILLANES GUEVARA MARIA BELEN</t>
+  </si>
+  <si>
+    <t>34915707</t>
+  </si>
+  <si>
+    <t>SAAVEDRA MARTINEZ MARIANA NOELIA</t>
+  </si>
+  <si>
+    <t>32454499</t>
+  </si>
+  <si>
+    <t>DIAZ CAADA CECILIA VANESA</t>
+  </si>
+  <si>
+    <t>31442398</t>
+  </si>
+  <si>
+    <t>FACHINETTI PAOLA MABEL BENITA</t>
+  </si>
+  <si>
+    <t>21362663</t>
+  </si>
+  <si>
+    <t>CAMACHO ADRIANA MONICA</t>
+  </si>
+  <si>
+    <t>22227369</t>
+  </si>
+  <si>
+    <t>TIZERA MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>21360428</t>
+  </si>
+  <si>
+    <t>YACANTE MERCADO FABIANA EDITH</t>
+  </si>
+  <si>
+    <t>39425712</t>
+  </si>
+  <si>
+    <t>QUIROGA SOLANGE MACARENA</t>
+  </si>
+  <si>
+    <t>34193855</t>
+  </si>
+  <si>
+    <t>LUNA LUCERO JOHANNA ELIZABETH</t>
+  </si>
+  <si>
+    <t>22159146</t>
+  </si>
+  <si>
+    <t>BUSTOS ADRIAN ALBERTO</t>
+  </si>
+  <si>
+    <t>42163190</t>
+  </si>
+  <si>
+    <t>BARAZA MENENDEZ FERNANDA GUADALUPE</t>
+  </si>
+  <si>
+    <t>34428246</t>
+  </si>
+  <si>
+    <t>GUERRERO MARIANELA CARINA</t>
+  </si>
+  <si>
+    <t>20655436</t>
+  </si>
+  <si>
+    <t>VIDELA FATIMA NELIDA</t>
+  </si>
+  <si>
+    <t>27617420</t>
+  </si>
+  <si>
+    <t>PUEBLA MACIAS JESICA ELVIRA</t>
+  </si>
+  <si>
+    <t>38594322</t>
+  </si>
+  <si>
+    <t>FERNANDEZ PEREZ FABIANA GRISELDA</t>
+  </si>
+  <si>
+    <t>26354224</t>
+  </si>
+  <si>
+    <t>RIOS ERICA NATALIA</t>
+  </si>
+  <si>
+    <t>31510070</t>
+  </si>
+  <si>
+    <t>OYOLA MORALES MAYRA VERONICA</t>
+  </si>
+  <si>
+    <t>25649373</t>
+  </si>
+  <si>
+    <t>QUILPATAY ANTONIA ANDREA</t>
+  </si>
+  <si>
+    <t>29621183</t>
+  </si>
+  <si>
+    <t>RETA TORRES DANIELA SOLEDAD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -403,14 +3027,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B442"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -418,28 +3042,3532 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>28855943</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>23977476</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>21212121</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>268</v>
+      </c>
+      <c r="B135" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>276</v>
+      </c>
+      <c r="B139" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>278</v>
+      </c>
+      <c r="B140" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>280</v>
+      </c>
+      <c r="B141" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>282</v>
+      </c>
+      <c r="B142" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>284</v>
+      </c>
+      <c r="B143" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>298</v>
+      </c>
+      <c r="B150" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>302</v>
+      </c>
+      <c r="B152" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>304</v>
+      </c>
+      <c r="B153" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>306</v>
+      </c>
+      <c r="B154" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>308</v>
+      </c>
+      <c r="B155" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>314</v>
+      </c>
+      <c r="B158" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+      <c r="B159" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B160" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>320</v>
+      </c>
+      <c r="B161" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>324</v>
+      </c>
+      <c r="B163" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>326</v>
+      </c>
+      <c r="B164" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>328</v>
+      </c>
+      <c r="B165" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>330</v>
+      </c>
+      <c r="B166" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>332</v>
+      </c>
+      <c r="B167" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>334</v>
+      </c>
+      <c r="B168" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>336</v>
+      </c>
+      <c r="B169" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>338</v>
+      </c>
+      <c r="B170" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>340</v>
+      </c>
+      <c r="B171" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>342</v>
+      </c>
+      <c r="B172" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>344</v>
+      </c>
+      <c r="B173" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>346</v>
+      </c>
+      <c r="B174" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>348</v>
+      </c>
+      <c r="B175" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>350</v>
+      </c>
+      <c r="B176" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>352</v>
+      </c>
+      <c r="B177" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>354</v>
+      </c>
+      <c r="B178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>356</v>
+      </c>
+      <c r="B179" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>358</v>
+      </c>
+      <c r="B180" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>360</v>
+      </c>
+      <c r="B181" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>362</v>
+      </c>
+      <c r="B182" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>364</v>
+      </c>
+      <c r="B183" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>366</v>
+      </c>
+      <c r="B184" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>368</v>
+      </c>
+      <c r="B185" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>370</v>
+      </c>
+      <c r="B186" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>372</v>
+      </c>
+      <c r="B187" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>374</v>
+      </c>
+      <c r="B188" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>376</v>
+      </c>
+      <c r="B189" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>378</v>
+      </c>
+      <c r="B190" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>380</v>
+      </c>
+      <c r="B191" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>382</v>
+      </c>
+      <c r="B192" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>384</v>
+      </c>
+      <c r="B193" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>386</v>
+      </c>
+      <c r="B194" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>388</v>
+      </c>
+      <c r="B195" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>390</v>
+      </c>
+      <c r="B196" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>392</v>
+      </c>
+      <c r="B197" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>394</v>
+      </c>
+      <c r="B198" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>396</v>
+      </c>
+      <c r="B199" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>398</v>
+      </c>
+      <c r="B200" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>400</v>
+      </c>
+      <c r="B201" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>402</v>
+      </c>
+      <c r="B202" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>404</v>
+      </c>
+      <c r="B203" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>406</v>
+      </c>
+      <c r="B204" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>408</v>
+      </c>
+      <c r="B205" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>410</v>
+      </c>
+      <c r="B206" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>412</v>
+      </c>
+      <c r="B207" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>414</v>
+      </c>
+      <c r="B208" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>416</v>
+      </c>
+      <c r="B209" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>418</v>
+      </c>
+      <c r="B210" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>420</v>
+      </c>
+      <c r="B211" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>422</v>
+      </c>
+      <c r="B212" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>424</v>
+      </c>
+      <c r="B213" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>426</v>
+      </c>
+      <c r="B214" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>428</v>
+      </c>
+      <c r="B215" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>430</v>
+      </c>
+      <c r="B216" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>432</v>
+      </c>
+      <c r="B217" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>434</v>
+      </c>
+      <c r="B218" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>436</v>
+      </c>
+      <c r="B219" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>438</v>
+      </c>
+      <c r="B220" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>440</v>
+      </c>
+      <c r="B221" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>442</v>
+      </c>
+      <c r="B222" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>444</v>
+      </c>
+      <c r="B223" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>446</v>
+      </c>
+      <c r="B224" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>448</v>
+      </c>
+      <c r="B225" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>450</v>
+      </c>
+      <c r="B226" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>452</v>
+      </c>
+      <c r="B227" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>454</v>
+      </c>
+      <c r="B228" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>456</v>
+      </c>
+      <c r="B229" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>458</v>
+      </c>
+      <c r="B230" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>460</v>
+      </c>
+      <c r="B231" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>462</v>
+      </c>
+      <c r="B232" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>464</v>
+      </c>
+      <c r="B233" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>466</v>
+      </c>
+      <c r="B234" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>468</v>
+      </c>
+      <c r="B235" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>470</v>
+      </c>
+      <c r="B236" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>472</v>
+      </c>
+      <c r="B237" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>474</v>
+      </c>
+      <c r="B238" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>476</v>
+      </c>
+      <c r="B239" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>478</v>
+      </c>
+      <c r="B240" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>480</v>
+      </c>
+      <c r="B241" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>482</v>
+      </c>
+      <c r="B242" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>484</v>
+      </c>
+      <c r="B243" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>486</v>
+      </c>
+      <c r="B244" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>488</v>
+      </c>
+      <c r="B245" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>490</v>
+      </c>
+      <c r="B246" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>492</v>
+      </c>
+      <c r="B247" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>494</v>
+      </c>
+      <c r="B248" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>496</v>
+      </c>
+      <c r="B249" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>498</v>
+      </c>
+      <c r="B250" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>500</v>
+      </c>
+      <c r="B251" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>502</v>
+      </c>
+      <c r="B252" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>504</v>
+      </c>
+      <c r="B253" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>506</v>
+      </c>
+      <c r="B254" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>508</v>
+      </c>
+      <c r="B255" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>510</v>
+      </c>
+      <c r="B256" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>512</v>
+      </c>
+      <c r="B257" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>514</v>
+      </c>
+      <c r="B258" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>516</v>
+      </c>
+      <c r="B259" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>518</v>
+      </c>
+      <c r="B260" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>520</v>
+      </c>
+      <c r="B261" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>522</v>
+      </c>
+      <c r="B262" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>524</v>
+      </c>
+      <c r="B263" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>526</v>
+      </c>
+      <c r="B264" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>528</v>
+      </c>
+      <c r="B265" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>530</v>
+      </c>
+      <c r="B266" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>532</v>
+      </c>
+      <c r="B267" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>534</v>
+      </c>
+      <c r="B268" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>536</v>
+      </c>
+      <c r="B269" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>538</v>
+      </c>
+      <c r="B270" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>540</v>
+      </c>
+      <c r="B271" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>542</v>
+      </c>
+      <c r="B272" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>544</v>
+      </c>
+      <c r="B273" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>546</v>
+      </c>
+      <c r="B274" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>548</v>
+      </c>
+      <c r="B275" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>550</v>
+      </c>
+      <c r="B276" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>552</v>
+      </c>
+      <c r="B277" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>554</v>
+      </c>
+      <c r="B278" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>556</v>
+      </c>
+      <c r="B279" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>558</v>
+      </c>
+      <c r="B280" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>560</v>
+      </c>
+      <c r="B281" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>562</v>
+      </c>
+      <c r="B282" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>564</v>
+      </c>
+      <c r="B283" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>566</v>
+      </c>
+      <c r="B284" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>568</v>
+      </c>
+      <c r="B285" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>570</v>
+      </c>
+      <c r="B286" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>572</v>
+      </c>
+      <c r="B287" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>574</v>
+      </c>
+      <c r="B288" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>576</v>
+      </c>
+      <c r="B289" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>578</v>
+      </c>
+      <c r="B290" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>580</v>
+      </c>
+      <c r="B291" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>582</v>
+      </c>
+      <c r="B292" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>584</v>
+      </c>
+      <c r="B293" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>586</v>
+      </c>
+      <c r="B294" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>588</v>
+      </c>
+      <c r="B295" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>590</v>
+      </c>
+      <c r="B296" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>592</v>
+      </c>
+      <c r="B297" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>594</v>
+      </c>
+      <c r="B298" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>596</v>
+      </c>
+      <c r="B299" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>598</v>
+      </c>
+      <c r="B300" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>600</v>
+      </c>
+      <c r="B301" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>602</v>
+      </c>
+      <c r="B302" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>604</v>
+      </c>
+      <c r="B303" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>606</v>
+      </c>
+      <c r="B304" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>608</v>
+      </c>
+      <c r="B305" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>610</v>
+      </c>
+      <c r="B306" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>612</v>
+      </c>
+      <c r="B307" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>614</v>
+      </c>
+      <c r="B308" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>616</v>
+      </c>
+      <c r="B309" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>618</v>
+      </c>
+      <c r="B310" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>620</v>
+      </c>
+      <c r="B311" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>622</v>
+      </c>
+      <c r="B312" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>624</v>
+      </c>
+      <c r="B313" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>626</v>
+      </c>
+      <c r="B314" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>628</v>
+      </c>
+      <c r="B315" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>630</v>
+      </c>
+      <c r="B316" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>632</v>
+      </c>
+      <c r="B317" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>634</v>
+      </c>
+      <c r="B318" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>636</v>
+      </c>
+      <c r="B319" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>638</v>
+      </c>
+      <c r="B320" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>640</v>
+      </c>
+      <c r="B321" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>642</v>
+      </c>
+      <c r="B322" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>644</v>
+      </c>
+      <c r="B323" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>646</v>
+      </c>
+      <c r="B324" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>648</v>
+      </c>
+      <c r="B325" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>650</v>
+      </c>
+      <c r="B326" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>652</v>
+      </c>
+      <c r="B327" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>654</v>
+      </c>
+      <c r="B328" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>656</v>
+      </c>
+      <c r="B329" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>658</v>
+      </c>
+      <c r="B330" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>660</v>
+      </c>
+      <c r="B331" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>662</v>
+      </c>
+      <c r="B332" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>664</v>
+      </c>
+      <c r="B333" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>666</v>
+      </c>
+      <c r="B334" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>370</v>
+      </c>
+      <c r="B335" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>668</v>
+      </c>
+      <c r="B336" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>392</v>
+      </c>
+      <c r="B337" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>670</v>
+      </c>
+      <c r="B338" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>672</v>
+      </c>
+      <c r="B339" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>674</v>
+      </c>
+      <c r="B340" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>676</v>
+      </c>
+      <c r="B341" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>678</v>
+      </c>
+      <c r="B342" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>680</v>
+      </c>
+      <c r="B343" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>682</v>
+      </c>
+      <c r="B344" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>684</v>
+      </c>
+      <c r="B345" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>686</v>
+      </c>
+      <c r="B346" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>688</v>
+      </c>
+      <c r="B347" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>690</v>
+      </c>
+      <c r="B348" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>692</v>
+      </c>
+      <c r="B349" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>694</v>
+      </c>
+      <c r="B350" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>696</v>
+      </c>
+      <c r="B351" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>698</v>
+      </c>
+      <c r="B352" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>700</v>
+      </c>
+      <c r="B353" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>702</v>
+      </c>
+      <c r="B354" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>704</v>
+      </c>
+      <c r="B355" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>706</v>
+      </c>
+      <c r="B356" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>708</v>
+      </c>
+      <c r="B357" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>710</v>
+      </c>
+      <c r="B358" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>712</v>
+      </c>
+      <c r="B359" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>714</v>
+      </c>
+      <c r="B360" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>716</v>
+      </c>
+      <c r="B361" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>718</v>
+      </c>
+      <c r="B362" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>720</v>
+      </c>
+      <c r="B363" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>722</v>
+      </c>
+      <c r="B364" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>724</v>
+      </c>
+      <c r="B365" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>726</v>
+      </c>
+      <c r="B366" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>728</v>
+      </c>
+      <c r="B367" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>730</v>
+      </c>
+      <c r="B368" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>732</v>
+      </c>
+      <c r="B369" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>734</v>
+      </c>
+      <c r="B370" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>736</v>
+      </c>
+      <c r="B371" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>738</v>
+      </c>
+      <c r="B372" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>740</v>
+      </c>
+      <c r="B373" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>742</v>
+      </c>
+      <c r="B374" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>744</v>
+      </c>
+      <c r="B375" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>746</v>
+      </c>
+      <c r="B376" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>748</v>
+      </c>
+      <c r="B377" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>750</v>
+      </c>
+      <c r="B378" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>752</v>
+      </c>
+      <c r="B379" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>754</v>
+      </c>
+      <c r="B380" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>756</v>
+      </c>
+      <c r="B381" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>758</v>
+      </c>
+      <c r="B382" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>760</v>
+      </c>
+      <c r="B383" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>762</v>
+      </c>
+      <c r="B384" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>764</v>
+      </c>
+      <c r="B385" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>766</v>
+      </c>
+      <c r="B386" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>768</v>
+      </c>
+      <c r="B387" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>770</v>
+      </c>
+      <c r="B388" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>772</v>
+      </c>
+      <c r="B389" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>774</v>
+      </c>
+      <c r="B390" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>776</v>
+      </c>
+      <c r="B391" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>778</v>
+      </c>
+      <c r="B392" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>780</v>
+      </c>
+      <c r="B393" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>782</v>
+      </c>
+      <c r="B394" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>784</v>
+      </c>
+      <c r="B395" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>786</v>
+      </c>
+      <c r="B396" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>788</v>
+      </c>
+      <c r="B397" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>790</v>
+      </c>
+      <c r="B398" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>792</v>
+      </c>
+      <c r="B399" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>794</v>
+      </c>
+      <c r="B400" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>796</v>
+      </c>
+      <c r="B401" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>798</v>
+      </c>
+      <c r="B402" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>800</v>
+      </c>
+      <c r="B403" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>802</v>
+      </c>
+      <c r="B404" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>804</v>
+      </c>
+      <c r="B405" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>806</v>
+      </c>
+      <c r="B406" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>808</v>
+      </c>
+      <c r="B407" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>810</v>
+      </c>
+      <c r="B408" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>812</v>
+      </c>
+      <c r="B409" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>814</v>
+      </c>
+      <c r="B410" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>816</v>
+      </c>
+      <c r="B411" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>818</v>
+      </c>
+      <c r="B412" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>820</v>
+      </c>
+      <c r="B413" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>822</v>
+      </c>
+      <c r="B414" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>824</v>
+      </c>
+      <c r="B415" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>826</v>
+      </c>
+      <c r="B416" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>828</v>
+      </c>
+      <c r="B417" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>830</v>
+      </c>
+      <c r="B418" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>832</v>
+      </c>
+      <c r="B419" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>834</v>
+      </c>
+      <c r="B420" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>836</v>
+      </c>
+      <c r="B421" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>838</v>
+      </c>
+      <c r="B422" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>840</v>
+      </c>
+      <c r="B423" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>842</v>
+      </c>
+      <c r="B424" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>844</v>
+      </c>
+      <c r="B425" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>846</v>
+      </c>
+      <c r="B426" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>848</v>
+      </c>
+      <c r="B427" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>850</v>
+      </c>
+      <c r="B428" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>852</v>
+      </c>
+      <c r="B429" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>854</v>
+      </c>
+      <c r="B430" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>856</v>
+      </c>
+      <c r="B431" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>858</v>
+      </c>
+      <c r="B432" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>860</v>
+      </c>
+      <c r="B433" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>862</v>
+      </c>
+      <c r="B434" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>864</v>
+      </c>
+      <c r="B435" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>866</v>
+      </c>
+      <c r="B436" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>868</v>
+      </c>
+      <c r="B437" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>870</v>
+      </c>
+      <c r="B438" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>872</v>
+      </c>
+      <c r="B439" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>874</v>
+      </c>
+      <c r="B440" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>876</v>
+      </c>
+      <c r="B441" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>878</v>
+      </c>
+      <c r="B442" t="s">
+        <v>879</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acreditaciones\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5448"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="8472"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="882">
   <si>
     <t>DNI</t>
   </si>
@@ -2675,6 +2675,12 @@
   </si>
   <si>
     <t>RETA TORRES DANIELA SOLEDAD</t>
+  </si>
+  <si>
+    <t>BUENO DIAZ MAIRA MELISA</t>
+  </si>
+  <si>
+    <t>VERA MARGARITA SABINA</t>
   </si>
 </sst>
 </file>
@@ -3028,10 +3034,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B442"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -6570,7 +6577,24 @@
         <v>879</v>
       </c>
     </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A443">
+        <v>32351130</v>
+      </c>
+      <c r="B443" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A444">
+        <v>22353650</v>
+      </c>
+      <c r="B444" t="s">
+        <v>881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\OneDrive\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="8472"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="8475"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -17,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="883">
   <si>
     <t>DNI</t>
   </si>
@@ -2681,12 +2676,15 @@
   </si>
   <si>
     <t>VERA MARGARITA SABINA</t>
+  </si>
+  <si>
+    <t>CABRERA MARGARITA FERNANDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3034,11 +3032,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B444"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B445"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -3049,7 +3047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3057,7 +3055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3065,7 +3063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3073,7 +3071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3081,7 +3079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3089,7 +3087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3097,7 +3095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3105,7 +3103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3113,7 +3111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3121,7 +3119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3129,7 +3127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3137,7 +3135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3145,7 +3143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3153,7 +3151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3161,7 +3159,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3169,7 +3167,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3177,7 +3175,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3185,7 +3183,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3193,7 +3191,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3201,7 +3199,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3209,7 +3207,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3217,7 +3215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -3225,7 +3223,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -3233,7 +3231,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -3241,7 +3239,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -3249,7 +3247,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -3257,7 +3255,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -3265,7 +3263,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -3273,7 +3271,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -3281,7 +3279,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -3289,7 +3287,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -3297,7 +3295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -3305,7 +3303,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -3313,7 +3311,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -3321,7 +3319,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -3329,7 +3327,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -3337,7 +3335,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -3345,7 +3343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -3353,7 +3351,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -3361,7 +3359,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -3369,7 +3367,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -3377,7 +3375,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -3385,7 +3383,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -3393,7 +3391,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -3401,7 +3399,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -3409,7 +3407,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -3417,7 +3415,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -3425,7 +3423,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -3433,7 +3431,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -3441,7 +3439,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -3449,7 +3447,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -3457,7 +3455,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -3465,7 +3463,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -3473,7 +3471,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -3481,7 +3479,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -3489,7 +3487,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -3497,7 +3495,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -3505,7 +3503,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -3513,7 +3511,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -3521,7 +3519,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -3529,7 +3527,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -3537,7 +3535,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -3545,7 +3543,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -3553,7 +3551,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>128</v>
       </c>
@@ -3561,7 +3559,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>130</v>
       </c>
@@ -3569,7 +3567,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>132</v>
       </c>
@@ -3577,7 +3575,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>134</v>
       </c>
@@ -3585,7 +3583,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -3593,7 +3591,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>138</v>
       </c>
@@ -3601,7 +3599,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>140</v>
       </c>
@@ -3609,7 +3607,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -3617,7 +3615,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -3625,7 +3623,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>146</v>
       </c>
@@ -3633,7 +3631,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>148</v>
       </c>
@@ -3641,7 +3639,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>150</v>
       </c>
@@ -3649,7 +3647,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>152</v>
       </c>
@@ -3657,7 +3655,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -3665,7 +3663,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>156</v>
       </c>
@@ -3673,7 +3671,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -3681,7 +3679,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -3689,7 +3687,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -3697,7 +3695,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -3705,7 +3703,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>166</v>
       </c>
@@ -3713,7 +3711,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>168</v>
       </c>
@@ -3721,7 +3719,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -3729,7 +3727,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>172</v>
       </c>
@@ -3737,7 +3735,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>174</v>
       </c>
@@ -3745,7 +3743,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -3753,7 +3751,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>178</v>
       </c>
@@ -3761,7 +3759,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>180</v>
       </c>
@@ -3769,7 +3767,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>182</v>
       </c>
@@ -3777,7 +3775,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>184</v>
       </c>
@@ -3785,7 +3783,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>186</v>
       </c>
@@ -3793,7 +3791,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>188</v>
       </c>
@@ -3801,7 +3799,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -3809,7 +3807,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -3817,7 +3815,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>194</v>
       </c>
@@ -3825,7 +3823,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>196</v>
       </c>
@@ -3833,7 +3831,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -3841,7 +3839,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>200</v>
       </c>
@@ -3849,7 +3847,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>202</v>
       </c>
@@ -3857,7 +3855,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -3865,7 +3863,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>206</v>
       </c>
@@ -3873,7 +3871,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>208</v>
       </c>
@@ -3881,7 +3879,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>210</v>
       </c>
@@ -3889,7 +3887,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>212</v>
       </c>
@@ -3897,7 +3895,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>214</v>
       </c>
@@ -3905,7 +3903,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -3913,7 +3911,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -3921,7 +3919,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>220</v>
       </c>
@@ -3929,7 +3927,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>222</v>
       </c>
@@ -3937,7 +3935,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>224</v>
       </c>
@@ -3945,7 +3943,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>226</v>
       </c>
@@ -3953,7 +3951,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -3961,7 +3959,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>230</v>
       </c>
@@ -3969,7 +3967,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -3977,7 +3975,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>234</v>
       </c>
@@ -3985,7 +3983,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>236</v>
       </c>
@@ -3993,7 +3991,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>238</v>
       </c>
@@ -4001,7 +3999,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -4009,7 +4007,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>242</v>
       </c>
@@ -4017,7 +4015,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -4025,7 +4023,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>246</v>
       </c>
@@ -4033,7 +4031,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>248</v>
       </c>
@@ -4041,7 +4039,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>250</v>
       </c>
@@ -4049,7 +4047,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>252</v>
       </c>
@@ -4057,7 +4055,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>254</v>
       </c>
@@ -4065,7 +4063,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>256</v>
       </c>
@@ -4073,7 +4071,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>258</v>
       </c>
@@ -4081,7 +4079,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>260</v>
       </c>
@@ -4089,7 +4087,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>262</v>
       </c>
@@ -4097,7 +4095,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>264</v>
       </c>
@@ -4105,7 +4103,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>266</v>
       </c>
@@ -4113,7 +4111,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>268</v>
       </c>
@@ -4121,7 +4119,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>270</v>
       </c>
@@ -4129,7 +4127,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>272</v>
       </c>
@@ -4137,7 +4135,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>274</v>
       </c>
@@ -4145,7 +4143,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>276</v>
       </c>
@@ -4153,7 +4151,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>278</v>
       </c>
@@ -4161,7 +4159,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -4169,7 +4167,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>282</v>
       </c>
@@ -4177,7 +4175,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>284</v>
       </c>
@@ -4185,7 +4183,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>286</v>
       </c>
@@ -4193,7 +4191,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>288</v>
       </c>
@@ -4201,7 +4199,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>290</v>
       </c>
@@ -4209,7 +4207,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>292</v>
       </c>
@@ -4217,7 +4215,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>294</v>
       </c>
@@ -4225,7 +4223,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>296</v>
       </c>
@@ -4233,7 +4231,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>298</v>
       </c>
@@ -4241,7 +4239,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>300</v>
       </c>
@@ -4249,7 +4247,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>302</v>
       </c>
@@ -4257,7 +4255,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>304</v>
       </c>
@@ -4265,7 +4263,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>306</v>
       </c>
@@ -4273,7 +4271,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>308</v>
       </c>
@@ -4281,7 +4279,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>310</v>
       </c>
@@ -4289,7 +4287,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>312</v>
       </c>
@@ -4297,7 +4295,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>314</v>
       </c>
@@ -4305,7 +4303,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>316</v>
       </c>
@@ -4313,7 +4311,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>318</v>
       </c>
@@ -4321,7 +4319,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>320</v>
       </c>
@@ -4329,7 +4327,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>322</v>
       </c>
@@ -4337,7 +4335,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>324</v>
       </c>
@@ -4345,7 +4343,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>326</v>
       </c>
@@ -4353,7 +4351,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>328</v>
       </c>
@@ -4361,7 +4359,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>330</v>
       </c>
@@ -4369,7 +4367,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>332</v>
       </c>
@@ -4377,7 +4375,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>334</v>
       </c>
@@ -4385,7 +4383,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -4393,7 +4391,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>338</v>
       </c>
@@ -4401,7 +4399,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>340</v>
       </c>
@@ -4409,7 +4407,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>342</v>
       </c>
@@ -4417,7 +4415,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>344</v>
       </c>
@@ -4425,7 +4423,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>346</v>
       </c>
@@ -4433,7 +4431,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>348</v>
       </c>
@@ -4441,7 +4439,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>350</v>
       </c>
@@ -4449,7 +4447,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>352</v>
       </c>
@@ -4457,7 +4455,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>354</v>
       </c>
@@ -4465,7 +4463,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>356</v>
       </c>
@@ -4473,7 +4471,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>358</v>
       </c>
@@ -4481,7 +4479,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>360</v>
       </c>
@@ -4489,7 +4487,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>362</v>
       </c>
@@ -4497,7 +4495,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>364</v>
       </c>
@@ -4505,7 +4503,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>366</v>
       </c>
@@ -4513,7 +4511,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>368</v>
       </c>
@@ -4521,7 +4519,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>370</v>
       </c>
@@ -4529,7 +4527,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>372</v>
       </c>
@@ -4537,7 +4535,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>374</v>
       </c>
@@ -4545,7 +4543,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>376</v>
       </c>
@@ -4553,7 +4551,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>378</v>
       </c>
@@ -4561,7 +4559,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>380</v>
       </c>
@@ -4569,7 +4567,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>382</v>
       </c>
@@ -4577,7 +4575,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>384</v>
       </c>
@@ -4585,7 +4583,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>386</v>
       </c>
@@ -4593,7 +4591,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>388</v>
       </c>
@@ -4601,7 +4599,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>390</v>
       </c>
@@ -4609,7 +4607,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>392</v>
       </c>
@@ -4617,7 +4615,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>394</v>
       </c>
@@ -4625,7 +4623,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>396</v>
       </c>
@@ -4633,7 +4631,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>398</v>
       </c>
@@ -4641,7 +4639,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>400</v>
       </c>
@@ -4649,7 +4647,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>402</v>
       </c>
@@ -4657,7 +4655,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>404</v>
       </c>
@@ -4665,7 +4663,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>406</v>
       </c>
@@ -4673,7 +4671,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>408</v>
       </c>
@@ -4681,7 +4679,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>410</v>
       </c>
@@ -4689,7 +4687,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>412</v>
       </c>
@@ -4697,7 +4695,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>414</v>
       </c>
@@ -4705,7 +4703,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>416</v>
       </c>
@@ -4713,7 +4711,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>418</v>
       </c>
@@ -4721,7 +4719,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>420</v>
       </c>
@@ -4729,7 +4727,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>422</v>
       </c>
@@ -4737,7 +4735,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>424</v>
       </c>
@@ -4745,7 +4743,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>426</v>
       </c>
@@ -4753,7 +4751,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>428</v>
       </c>
@@ -4761,7 +4759,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>430</v>
       </c>
@@ -4769,7 +4767,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>432</v>
       </c>
@@ -4777,7 +4775,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>434</v>
       </c>
@@ -4785,7 +4783,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>436</v>
       </c>
@@ -4793,7 +4791,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>438</v>
       </c>
@@ -4801,7 +4799,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>440</v>
       </c>
@@ -4809,7 +4807,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>442</v>
       </c>
@@ -4817,7 +4815,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>444</v>
       </c>
@@ -4825,7 +4823,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>446</v>
       </c>
@@ -4833,7 +4831,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>448</v>
       </c>
@@ -4841,7 +4839,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>450</v>
       </c>
@@ -4849,7 +4847,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>452</v>
       </c>
@@ -4857,7 +4855,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>454</v>
       </c>
@@ -4865,7 +4863,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>456</v>
       </c>
@@ -4873,7 +4871,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>458</v>
       </c>
@@ -4881,7 +4879,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>460</v>
       </c>
@@ -4889,7 +4887,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>462</v>
       </c>
@@ -4897,7 +4895,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>464</v>
       </c>
@@ -4905,7 +4903,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>466</v>
       </c>
@@ -4913,7 +4911,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>468</v>
       </c>
@@ -4921,7 +4919,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>470</v>
       </c>
@@ -4929,7 +4927,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>472</v>
       </c>
@@ -4937,7 +4935,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>474</v>
       </c>
@@ -4945,7 +4943,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>476</v>
       </c>
@@ -4953,7 +4951,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>478</v>
       </c>
@@ -4961,7 +4959,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>480</v>
       </c>
@@ -4969,7 +4967,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>482</v>
       </c>
@@ -4977,7 +4975,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>484</v>
       </c>
@@ -4985,7 +4983,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>486</v>
       </c>
@@ -4993,7 +4991,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>488</v>
       </c>
@@ -5001,7 +4999,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>490</v>
       </c>
@@ -5009,7 +5007,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>492</v>
       </c>
@@ -5017,7 +5015,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>494</v>
       </c>
@@ -5025,7 +5023,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>496</v>
       </c>
@@ -5033,7 +5031,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>498</v>
       </c>
@@ -5041,7 +5039,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>500</v>
       </c>
@@ -5049,7 +5047,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>502</v>
       </c>
@@ -5057,7 +5055,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>504</v>
       </c>
@@ -5065,7 +5063,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>506</v>
       </c>
@@ -5073,7 +5071,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>508</v>
       </c>
@@ -5081,7 +5079,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>510</v>
       </c>
@@ -5089,7 +5087,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>512</v>
       </c>
@@ -5097,7 +5095,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>514</v>
       </c>
@@ -5105,7 +5103,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>516</v>
       </c>
@@ -5113,7 +5111,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>518</v>
       </c>
@@ -5121,7 +5119,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>520</v>
       </c>
@@ -5129,7 +5127,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>522</v>
       </c>
@@ -5137,7 +5135,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>524</v>
       </c>
@@ -5145,7 +5143,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>526</v>
       </c>
@@ -5153,7 +5151,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>528</v>
       </c>
@@ -5161,7 +5159,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>530</v>
       </c>
@@ -5169,7 +5167,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>532</v>
       </c>
@@ -5177,7 +5175,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>534</v>
       </c>
@@ -5185,7 +5183,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>536</v>
       </c>
@@ -5193,7 +5191,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>538</v>
       </c>
@@ -5201,7 +5199,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>540</v>
       </c>
@@ -5209,7 +5207,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>542</v>
       </c>
@@ -5217,7 +5215,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>544</v>
       </c>
@@ -5225,7 +5223,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>546</v>
       </c>
@@ -5233,7 +5231,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>548</v>
       </c>
@@ -5241,7 +5239,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>550</v>
       </c>
@@ -5249,7 +5247,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>552</v>
       </c>
@@ -5257,7 +5255,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>554</v>
       </c>
@@ -5265,7 +5263,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>556</v>
       </c>
@@ -5273,7 +5271,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>558</v>
       </c>
@@ -5281,7 +5279,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>560</v>
       </c>
@@ -5289,7 +5287,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>562</v>
       </c>
@@ -5297,7 +5295,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>564</v>
       </c>
@@ -5305,7 +5303,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>566</v>
       </c>
@@ -5313,7 +5311,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>568</v>
       </c>
@@ -5321,7 +5319,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>570</v>
       </c>
@@ -5329,7 +5327,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>572</v>
       </c>
@@ -5337,7 +5335,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>574</v>
       </c>
@@ -5345,7 +5343,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>576</v>
       </c>
@@ -5353,7 +5351,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>578</v>
       </c>
@@ -5361,7 +5359,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>580</v>
       </c>
@@ -5369,7 +5367,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>582</v>
       </c>
@@ -5377,7 +5375,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>584</v>
       </c>
@@ -5385,7 +5383,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>586</v>
       </c>
@@ -5393,7 +5391,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>588</v>
       </c>
@@ -5401,7 +5399,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>590</v>
       </c>
@@ -5409,7 +5407,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>592</v>
       </c>
@@ -5417,7 +5415,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>594</v>
       </c>
@@ -5425,7 +5423,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>596</v>
       </c>
@@ -5433,7 +5431,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>598</v>
       </c>
@@ -5441,7 +5439,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>600</v>
       </c>
@@ -5449,7 +5447,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>602</v>
       </c>
@@ -5457,7 +5455,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>604</v>
       </c>
@@ -5465,7 +5463,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>606</v>
       </c>
@@ -5473,7 +5471,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>608</v>
       </c>
@@ -5481,7 +5479,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>610</v>
       </c>
@@ -5489,7 +5487,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>612</v>
       </c>
@@ -5497,7 +5495,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>614</v>
       </c>
@@ -5505,7 +5503,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>616</v>
       </c>
@@ -5513,7 +5511,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>618</v>
       </c>
@@ -5521,7 +5519,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>620</v>
       </c>
@@ -5529,7 +5527,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>622</v>
       </c>
@@ -5537,7 +5535,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>624</v>
       </c>
@@ -5545,7 +5543,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>626</v>
       </c>
@@ -5553,7 +5551,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>628</v>
       </c>
@@ -5561,7 +5559,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>630</v>
       </c>
@@ -5569,7 +5567,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>632</v>
       </c>
@@ -5577,7 +5575,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>634</v>
       </c>
@@ -5585,7 +5583,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>636</v>
       </c>
@@ -5593,7 +5591,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>638</v>
       </c>
@@ -5601,7 +5599,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>640</v>
       </c>
@@ -5609,7 +5607,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>642</v>
       </c>
@@ -5617,7 +5615,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>644</v>
       </c>
@@ -5625,7 +5623,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>646</v>
       </c>
@@ -5633,7 +5631,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>648</v>
       </c>
@@ -5641,7 +5639,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>650</v>
       </c>
@@ -5649,7 +5647,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>652</v>
       </c>
@@ -5657,7 +5655,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>654</v>
       </c>
@@ -5665,7 +5663,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>656</v>
       </c>
@@ -5673,7 +5671,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>658</v>
       </c>
@@ -5681,7 +5679,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>660</v>
       </c>
@@ -5689,7 +5687,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>662</v>
       </c>
@@ -5697,7 +5695,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>664</v>
       </c>
@@ -5705,7 +5703,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>666</v>
       </c>
@@ -5713,7 +5711,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>370</v>
       </c>
@@ -5721,7 +5719,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>668</v>
       </c>
@@ -5729,7 +5727,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>392</v>
       </c>
@@ -5737,7 +5735,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>670</v>
       </c>
@@ -5745,7 +5743,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>672</v>
       </c>
@@ -5753,7 +5751,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>674</v>
       </c>
@@ -5761,7 +5759,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>676</v>
       </c>
@@ -5769,7 +5767,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>678</v>
       </c>
@@ -5777,7 +5775,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>680</v>
       </c>
@@ -5785,7 +5783,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>682</v>
       </c>
@@ -5793,7 +5791,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>684</v>
       </c>
@@ -5801,7 +5799,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>686</v>
       </c>
@@ -5809,7 +5807,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>688</v>
       </c>
@@ -5817,7 +5815,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>690</v>
       </c>
@@ -5825,7 +5823,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>692</v>
       </c>
@@ -5833,7 +5831,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>694</v>
       </c>
@@ -5841,7 +5839,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>696</v>
       </c>
@@ -5849,7 +5847,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>698</v>
       </c>
@@ -5857,7 +5855,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>700</v>
       </c>
@@ -5865,7 +5863,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>702</v>
       </c>
@@ -5873,7 +5871,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>704</v>
       </c>
@@ -5881,7 +5879,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>706</v>
       </c>
@@ -5889,7 +5887,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>708</v>
       </c>
@@ -5897,7 +5895,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>710</v>
       </c>
@@ -5905,7 +5903,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>712</v>
       </c>
@@ -5913,7 +5911,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>714</v>
       </c>
@@ -5921,7 +5919,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>716</v>
       </c>
@@ -5929,7 +5927,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>718</v>
       </c>
@@ -5937,7 +5935,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>720</v>
       </c>
@@ -5945,7 +5943,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>722</v>
       </c>
@@ -5953,7 +5951,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>724</v>
       </c>
@@ -5961,7 +5959,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>726</v>
       </c>
@@ -5969,7 +5967,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>728</v>
       </c>
@@ -5977,7 +5975,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>730</v>
       </c>
@@ -5985,7 +5983,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>732</v>
       </c>
@@ -5993,7 +5991,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>734</v>
       </c>
@@ -6001,7 +5999,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>736</v>
       </c>
@@ -6009,7 +6007,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>738</v>
       </c>
@@ -6017,7 +6015,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>740</v>
       </c>
@@ -6025,7 +6023,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>742</v>
       </c>
@@ -6033,7 +6031,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>744</v>
       </c>
@@ -6041,7 +6039,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>746</v>
       </c>
@@ -6049,7 +6047,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>748</v>
       </c>
@@ -6057,7 +6055,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>750</v>
       </c>
@@ -6065,7 +6063,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>752</v>
       </c>
@@ -6073,7 +6071,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>754</v>
       </c>
@@ -6081,7 +6079,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>756</v>
       </c>
@@ -6089,7 +6087,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>758</v>
       </c>
@@ -6097,7 +6095,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>760</v>
       </c>
@@ -6105,7 +6103,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>762</v>
       </c>
@@ -6113,7 +6111,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>764</v>
       </c>
@@ -6121,7 +6119,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>766</v>
       </c>
@@ -6129,7 +6127,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>768</v>
       </c>
@@ -6137,7 +6135,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>770</v>
       </c>
@@ -6145,7 +6143,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>772</v>
       </c>
@@ -6153,7 +6151,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>774</v>
       </c>
@@ -6161,7 +6159,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>776</v>
       </c>
@@ -6169,7 +6167,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>778</v>
       </c>
@@ -6177,7 +6175,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>780</v>
       </c>
@@ -6185,7 +6183,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>782</v>
       </c>
@@ -6193,7 +6191,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>784</v>
       </c>
@@ -6201,7 +6199,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>786</v>
       </c>
@@ -6209,7 +6207,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>788</v>
       </c>
@@ -6217,7 +6215,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>790</v>
       </c>
@@ -6225,7 +6223,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>792</v>
       </c>
@@ -6233,7 +6231,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>794</v>
       </c>
@@ -6241,7 +6239,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>796</v>
       </c>
@@ -6249,7 +6247,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>798</v>
       </c>
@@ -6257,7 +6255,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>800</v>
       </c>
@@ -6265,7 +6263,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>802</v>
       </c>
@@ -6273,7 +6271,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>804</v>
       </c>
@@ -6281,7 +6279,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>806</v>
       </c>
@@ -6289,7 +6287,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>808</v>
       </c>
@@ -6297,7 +6295,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>810</v>
       </c>
@@ -6305,7 +6303,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>812</v>
       </c>
@@ -6313,7 +6311,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>814</v>
       </c>
@@ -6321,7 +6319,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>816</v>
       </c>
@@ -6329,7 +6327,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>818</v>
       </c>
@@ -6337,7 +6335,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>820</v>
       </c>
@@ -6345,7 +6343,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>822</v>
       </c>
@@ -6353,7 +6351,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>824</v>
       </c>
@@ -6361,7 +6359,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>826</v>
       </c>
@@ -6369,7 +6367,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>828</v>
       </c>
@@ -6377,7 +6375,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>830</v>
       </c>
@@ -6385,7 +6383,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>832</v>
       </c>
@@ -6393,7 +6391,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>834</v>
       </c>
@@ -6401,7 +6399,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>836</v>
       </c>
@@ -6409,7 +6407,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>838</v>
       </c>
@@ -6417,7 +6415,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>840</v>
       </c>
@@ -6425,7 +6423,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>842</v>
       </c>
@@ -6433,7 +6431,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>844</v>
       </c>
@@ -6441,7 +6439,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>846</v>
       </c>
@@ -6449,7 +6447,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>848</v>
       </c>
@@ -6457,7 +6455,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>850</v>
       </c>
@@ -6465,7 +6463,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>852</v>
       </c>
@@ -6473,7 +6471,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>854</v>
       </c>
@@ -6481,7 +6479,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>856</v>
       </c>
@@ -6489,7 +6487,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>858</v>
       </c>
@@ -6497,7 +6495,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>860</v>
       </c>
@@ -6505,7 +6503,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>862</v>
       </c>
@@ -6513,7 +6511,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>864</v>
       </c>
@@ -6521,7 +6519,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>866</v>
       </c>
@@ -6529,7 +6527,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>868</v>
       </c>
@@ -6537,7 +6535,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>870</v>
       </c>
@@ -6545,7 +6543,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>872</v>
       </c>
@@ -6553,7 +6551,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>874</v>
       </c>
@@ -6561,7 +6559,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>876</v>
       </c>
@@ -6569,7 +6567,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>878</v>
       </c>
@@ -6577,7 +6575,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>32351130</v>
       </c>
@@ -6585,12 +6583,20 @@
         <v>880</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>22353650</v>
       </c>
       <c r="B444" t="s">
         <v>881</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>25938790</v>
+      </c>
+      <c r="B445" t="s">
+        <v>882</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -2678,7 +2678,7 @@
     <t>VERA MARGARITA SABINA</t>
   </si>
   <si>
-    <t>CABRERA MARGARITA FERNANDA</t>
+    <t>CABRERA MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
